--- a/internal_doc/05.测试设计/可靠性测试/基本操作故障测试.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/基本操作故障测试.xlsx
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="325">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -834,58 +834,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cata主节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>连接的coord故障</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>处理操作的节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>断网</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点故障&lt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点故障&gt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备节点故障&gt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备节点故障&lt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>处理操作的节点故障&lt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>处理操作的节点故障&gt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CPU耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -910,10 +866,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据组节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>数据库节点故障</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1011,18 +963,6 @@
     <t>连接的coord拥塞大于超时时间，如35s</t>
   </si>
   <si>
-    <t>w=2时两个备节点故障</t>
-  </si>
-  <si>
-    <t>w=2时两个备节点故障&lt;超时时间</t>
-  </si>
-  <si>
-    <t>w=2时两个备节点故障&gt;超时时间</t>
-  </si>
-  <si>
-    <t>比上一个场景多了：w=2时两个备节点故障</t>
-  </si>
-  <si>
     <t>数据节点故障</t>
   </si>
   <si>
@@ -1096,15 +1036,272 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时间频繁跳变后，备节点主机正常常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>h3g3d7时连续降备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>h3g3d7时连续降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点断网</t>
+  </si>
+  <si>
+    <t>处理操作的节点断网</t>
+  </si>
+  <si>
+    <t>备节点断网</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点断网</t>
+  </si>
+  <si>
+    <t>cata主节点断网</t>
+  </si>
+  <si>
+    <t>连接的coord断网</t>
+  </si>
+  <si>
+    <t>主节点闪断&lt;超时时间</t>
+  </si>
+  <si>
+    <t>处理操作的节点闪断&lt;超时时间</t>
+  </si>
+  <si>
+    <t>主节点闪断&gt;超时时间</t>
+  </si>
+  <si>
+    <t>处理操作的节点闪断&gt;超时时间</t>
+  </si>
+  <si>
+    <t>备节点闪断&lt;超时时间</t>
+  </si>
+  <si>
+    <t>备节点闪断&gt;超时时间</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点闪断&lt;超时时间</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点闪断&gt;超时时间</t>
+  </si>
+  <si>
+    <t>连接的coord闪断&lt;超时时间</t>
+  </si>
+  <si>
+    <t>连接的coord闪断&gt;超时时间</t>
+  </si>
+  <si>
+    <t>主节点拥塞&lt;超时时间</t>
+  </si>
+  <si>
+    <t>处理操作的节点拥塞&lt;超时时间</t>
+  </si>
+  <si>
+    <t>主节点拥塞&gt;超时时间</t>
+  </si>
+  <si>
+    <t>处理操作的节点拥塞&gt;超时时间</t>
+  </si>
+  <si>
+    <t>备节点拥塞&lt;超时时间</t>
+  </si>
+  <si>
+    <t>备节点拥塞&gt;超时时间</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点拥塞&lt;超时时间</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点拥塞&gt;超时时间</t>
+  </si>
+  <si>
+    <t>连接的coord拥塞&lt;超时时间</t>
+  </si>
+  <si>
+    <t>连接的coord拥塞&gt;超时时间</t>
+  </si>
+  <si>
+    <t>主节点CPU耗尽</t>
+  </si>
+  <si>
+    <t>处理操作的节点CPU耗尽</t>
+  </si>
+  <si>
+    <t>备节点CPU耗尽</t>
+  </si>
+  <si>
+    <t>主节点内存耗尽</t>
+  </si>
+  <si>
+    <t>处理操作的节点内存耗尽</t>
+  </si>
+  <si>
+    <t>备节点内存耗尽</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点内存耗尽</t>
+  </si>
+  <si>
+    <t>主节点磁盘满</t>
+  </si>
+  <si>
+    <t>处理操作的节点磁盘满</t>
+  </si>
+  <si>
+    <t>备节点磁盘满</t>
+  </si>
+  <si>
+    <t>主节点umount盘</t>
+  </si>
+  <si>
+    <t>处理操作的节点umount盘</t>
+  </si>
+  <si>
+    <t>备节点umount盘</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点umount盘</t>
+  </si>
+  <si>
+    <t>主节点磁盘损坏</t>
+  </si>
+  <si>
+    <t>处理操作的节点磁盘损坏</t>
+  </si>
+  <si>
+    <t>备节点磁盘损坏</t>
+  </si>
+  <si>
+    <t>主节点时间跳变</t>
+  </si>
+  <si>
+    <t>处理操作的节点时间跳变</t>
+  </si>
+  <si>
+    <t>备节点时间跳变</t>
+  </si>
+  <si>
+    <t>cata主节点时间跳变</t>
+  </si>
+  <si>
+    <t>连接的coord时间跳变</t>
+  </si>
+  <si>
+    <t>主节点正常重启</t>
+  </si>
+  <si>
+    <t>处理操作的节点正常重启</t>
+  </si>
+  <si>
+    <t>备节点正常重启</t>
+  </si>
+  <si>
+    <t>cata主节点正常重启</t>
+  </si>
+  <si>
+    <t>连接的coord正常重启</t>
+  </si>
+  <si>
+    <t>数据组节点正常重启</t>
+  </si>
+  <si>
+    <t>数据库节点正常重启</t>
+  </si>
+  <si>
+    <t>主节点异常重启</t>
+  </si>
+  <si>
+    <t>处理操作的节点异常重启</t>
+  </si>
+  <si>
+    <t>比上一个场景多了：w=2时两个备节点异常重启</t>
+  </si>
+  <si>
+    <t>备节点异常重启</t>
+  </si>
+  <si>
+    <t>cata主节点异常重启</t>
+  </si>
+  <si>
+    <t>连接的coord异常重启</t>
+  </si>
+  <si>
+    <t>数据组节点异常重启</t>
+  </si>
+  <si>
+    <t>数据库节点异常重启</t>
+  </si>
+  <si>
+    <t>主节点主机正常重启</t>
+  </si>
+  <si>
+    <t>处理操作的节点主机正常重启</t>
+  </si>
+  <si>
+    <t>备节点主机正常重启</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点主机正常重启</t>
+  </si>
+  <si>
+    <t>cata主节点主机正常重启</t>
+  </si>
+  <si>
+    <t>连接的coord主机正常重启</t>
+  </si>
+  <si>
+    <t>数据组节点主机正常重启</t>
+  </si>
+  <si>
+    <t>数据库节点主机正常重启</t>
+  </si>
+  <si>
+    <t>主节点主机异常重启</t>
+  </si>
+  <si>
+    <t>处理操作的节点主机异常重启</t>
+  </si>
+  <si>
+    <t>备节点主机异常重启</t>
+  </si>
+  <si>
+    <t>w=2时两个备节点主机异常重启</t>
+  </si>
+  <si>
+    <t>cata主节点主机异常重启</t>
+  </si>
+  <si>
+    <t>连接的coord主机异常重启</t>
+  </si>
+  <si>
+    <t>数据组节点主机异常重启</t>
+  </si>
+  <si>
+    <t>数据库节点主机异常重启</t>
+  </si>
+  <si>
+    <t>主节点闪断&lt;超时时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据组节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=2时两个备节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间延后，主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间提前，备节点主机异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1112,7 +1309,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1181,8 +1378,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1211,6 +1416,11 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1392,10 +1602,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1447,9 +1660,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1459,17 +1674,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,17 +1694,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1908,13 +2123,13 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="65" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="4"/>
@@ -1924,7 +2139,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="49"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1938,9 +2153,9 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="49"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -1950,7 +2165,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="49"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
@@ -1968,9 +2183,9 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="50"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>24</v>
@@ -1984,7 +2199,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="52" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -2000,7 +2215,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="49"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -2014,9 +2229,9 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="49"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -2026,7 +2241,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="49"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2042,9 +2257,9 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="50"/>
+      <c r="D12" s="54"/>
       <c r="E12" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2112,7 +2327,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -2128,9 +2343,9 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="51"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="5" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -2140,7 +2355,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="52"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="13" t="s">
         <v>134</v>
       </c>
@@ -2158,7 +2373,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>138</v>
@@ -2190,7 +2405,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -2264,7 +2479,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -2322,7 +2537,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -2338,7 +2553,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="49"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="5" t="s">
         <v>145</v>
       </c>
@@ -2352,7 +2567,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="49"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="5" t="s">
         <v>142</v>
       </c>
@@ -2366,7 +2581,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="49"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="5" t="s">
         <v>146</v>
       </c>
@@ -2384,9 +2599,9 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="49"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -2396,9 +2611,9 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="49"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -2408,7 +2623,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="49"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="5" t="s">
         <v>151</v>
       </c>
@@ -2422,9 +2637,9 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="50"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>24</v>
@@ -2440,7 +2655,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -2456,7 +2671,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="49"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="5" t="s">
         <v>145</v>
       </c>
@@ -2470,7 +2685,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="49"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="5" t="s">
         <v>143</v>
       </c>
@@ -2484,7 +2699,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="49"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="5" t="s">
         <v>146</v>
       </c>
@@ -2498,9 +2713,9 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="49"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -2510,9 +2725,9 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="49"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -2522,9 +2737,9 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="49"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -2534,9 +2749,9 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="50"/>
+      <c r="D45" s="54"/>
       <c r="E45" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
@@ -2588,7 +2803,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -2600,7 +2815,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -2626,7 +2841,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>24</v>
@@ -2642,7 +2857,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="53" t="s">
+      <c r="D52" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -2658,7 +2873,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="4" t="s">
         <v>147</v>
       </c>
@@ -2672,7 +2887,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
@@ -2684,9 +2899,9 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="52"/>
+      <c r="D55" s="57"/>
       <c r="E55" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
@@ -2766,7 +2981,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -2778,7 +2993,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -2804,7 +3019,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>88</v>
@@ -2878,7 +3093,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -2890,7 +3105,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -2902,7 +3117,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -2914,7 +3129,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -2942,7 +3157,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -2958,7 +3173,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="49"/>
+      <c r="D74" s="53"/>
       <c r="E74" s="5" t="s">
         <v>148</v>
       </c>
@@ -2972,7 +3187,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="49"/>
+      <c r="D75" s="53"/>
       <c r="E75" s="5" t="s">
         <v>153</v>
       </c>
@@ -2986,7 +3201,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="49"/>
+      <c r="D76" s="53"/>
       <c r="E76" s="5" t="s">
         <v>149</v>
       </c>
@@ -3000,9 +3215,9 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="49"/>
+      <c r="D77" s="53"/>
       <c r="E77" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -3012,9 +3227,9 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="49"/>
+      <c r="D78" s="53"/>
       <c r="E78" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -3024,7 +3239,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="49"/>
+      <c r="D79" s="53"/>
       <c r="E79" s="13" t="s">
         <v>154</v>
       </c>
@@ -3038,9 +3253,9 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="50"/>
+      <c r="D80" s="54"/>
       <c r="E80" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>24</v>
@@ -3054,7 +3269,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="48" t="s">
+      <c r="D81" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -3068,7 +3283,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="49"/>
+      <c r="D82" s="53"/>
       <c r="E82" s="5" t="s">
         <v>148</v>
       </c>
@@ -3080,7 +3295,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="49"/>
+      <c r="D83" s="53"/>
       <c r="E83" s="5" t="s">
         <v>143</v>
       </c>
@@ -3092,7 +3307,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="49"/>
+      <c r="D84" s="53"/>
       <c r="E84" s="5" t="s">
         <v>149</v>
       </c>
@@ -3104,9 +3319,9 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="49"/>
+      <c r="D85" s="53"/>
       <c r="E85" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
@@ -3118,9 +3333,9 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="49"/>
+      <c r="D86" s="53"/>
       <c r="E86" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -3130,7 +3345,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="49"/>
+      <c r="D87" s="53"/>
       <c r="E87" s="13" t="s">
         <v>154</v>
       </c>
@@ -3142,9 +3357,9 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="50"/>
+      <c r="D88" s="54"/>
       <c r="E88" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -3190,7 +3405,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
@@ -3204,7 +3419,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -3230,7 +3445,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -3244,7 +3459,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="53" t="s">
+      <c r="D95" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -3260,7 +3475,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="51"/>
+      <c r="D96" s="56"/>
       <c r="E96" s="4" t="s">
         <v>150</v>
       </c>
@@ -3272,7 +3487,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="51"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="13" t="s">
         <v>154</v>
       </c>
@@ -3284,9 +3499,9 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="52"/>
+      <c r="D98" s="57"/>
       <c r="E98" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -3358,7 +3573,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -3370,7 +3585,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -3398,7 +3613,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>88</v>
@@ -3462,7 +3677,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -3474,7 +3689,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -3498,7 +3713,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -3524,7 +3739,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="48" t="s">
+      <c r="D116" s="52" t="s">
         <v>128</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -3544,7 +3759,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="49"/>
+      <c r="D117" s="53"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -3562,7 +3777,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="50"/>
+      <c r="D118" s="54"/>
       <c r="E118" s="6" t="s">
         <v>156</v>
       </c>
@@ -3578,7 +3793,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="48" t="s">
+      <c r="D119" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -3592,7 +3807,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="49"/>
+      <c r="D120" s="53"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -3604,7 +3819,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="50"/>
+      <c r="D121" s="54"/>
       <c r="E121" s="6" t="s">
         <v>156</v>
       </c>
@@ -3744,7 +3959,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="48" t="s">
+      <c r="D131" s="52" t="s">
         <v>128</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -3762,7 +3977,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="49"/>
+      <c r="D132" s="53"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -3778,7 +3993,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="50"/>
+      <c r="D133" s="54"/>
       <c r="E133" s="6" t="s">
         <v>156</v>
       </c>
@@ -3794,7 +4009,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="48" t="s">
+      <c r="D134" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -3808,7 +4023,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="49"/>
+      <c r="D135" s="53"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -3820,7 +4035,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="50"/>
+      <c r="D136" s="54"/>
       <c r="E136" s="6" t="s">
         <v>156</v>
       </c>
@@ -3960,7 +4175,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="48" t="s">
+      <c r="D146" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -3980,7 +4195,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="49"/>
+      <c r="D147" s="53"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -3996,7 +4211,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="49"/>
+      <c r="D148" s="53"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -4008,7 +4223,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="50"/>
+      <c r="D149" s="54"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -4022,7 +4237,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="48" t="s">
+      <c r="D150" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -4036,7 +4251,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="49"/>
+      <c r="D151" s="53"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -4048,7 +4263,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="49"/>
+      <c r="D152" s="53"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -4060,7 +4275,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="50"/>
+      <c r="D153" s="54"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -4116,7 +4331,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="48" t="s">
+      <c r="D157" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -4130,7 +4345,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="49"/>
+      <c r="D158" s="53"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -4142,7 +4357,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="50"/>
+      <c r="D159" s="54"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -4380,7 +4595,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="48" t="s">
+      <c r="D176" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -4396,7 +4611,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="49"/>
+      <c r="D177" s="53"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -4410,7 +4625,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="50"/>
+      <c r="D178" s="54"/>
       <c r="E178" s="6" t="s">
         <v>157</v>
       </c>
@@ -4426,7 +4641,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="48" t="s">
+      <c r="D179" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -4440,7 +4655,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="49"/>
+      <c r="D180" s="53"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -4452,7 +4667,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="50"/>
+      <c r="D181" s="54"/>
       <c r="E181" s="6" t="s">
         <v>157</v>
       </c>
@@ -4596,7 +4811,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="48" t="s">
+      <c r="D191" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -4612,7 +4827,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="49"/>
+      <c r="D192" s="53"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -4626,7 +4841,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="49"/>
+      <c r="D193" s="53"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -4640,7 +4855,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="49"/>
+      <c r="D194" s="53"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -4654,7 +4869,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="49"/>
+      <c r="D195" s="53"/>
       <c r="E195" s="13" t="s">
         <v>48</v>
       </c>
@@ -4670,7 +4885,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="50"/>
+      <c r="D196" s="54"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -4688,7 +4903,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="48" t="s">
+      <c r="D197" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -4702,7 +4917,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="49"/>
+      <c r="D198" s="53"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -4714,7 +4929,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="49"/>
+      <c r="D199" s="53"/>
       <c r="E199" s="6" t="s">
         <v>158</v>
       </c>
@@ -4726,7 +4941,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="49"/>
+      <c r="D200" s="53"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -4738,7 +4953,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="49"/>
+      <c r="D201" s="53"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -4750,7 +4965,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="49"/>
+      <c r="D202" s="53"/>
       <c r="E202" s="13" t="s">
         <v>163</v>
       </c>
@@ -4764,7 +4979,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="50"/>
+      <c r="D203" s="54"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -4858,7 +5073,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="48" t="s">
+      <c r="D209" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -4872,7 +5087,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="49"/>
+      <c r="D210" s="53"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -4884,7 +5099,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="49"/>
+      <c r="D211" s="53"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -4896,7 +5111,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="49"/>
+      <c r="D212" s="53"/>
       <c r="E212" s="13" t="s">
         <v>163</v>
       </c>
@@ -4910,7 +5125,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="50"/>
+      <c r="D213" s="54"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -5108,7 +5323,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="48" t="s">
+      <c r="D227" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -5124,7 +5339,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="49"/>
+      <c r="D228" s="53"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -5138,7 +5353,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="49"/>
+      <c r="D229" s="53"/>
       <c r="E229" s="6" t="s">
         <v>159</v>
       </c>
@@ -5152,7 +5367,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="49"/>
+      <c r="D230" s="53"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -5166,7 +5381,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="49"/>
+      <c r="D231" s="53"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -5180,7 +5395,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="49"/>
+      <c r="D232" s="53"/>
       <c r="E232" s="13" t="s">
         <v>167</v>
       </c>
@@ -5194,7 +5409,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="50"/>
+      <c r="D233" s="54"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -5210,7 +5425,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="48" t="s">
+      <c r="D234" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -5224,7 +5439,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="49"/>
+      <c r="D235" s="53"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -5236,7 +5451,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="49"/>
+      <c r="D236" s="53"/>
       <c r="E236" s="6" t="s">
         <v>159</v>
       </c>
@@ -5248,7 +5463,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="49"/>
+      <c r="D237" s="53"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -5260,7 +5475,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="49"/>
+      <c r="D238" s="53"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -5272,7 +5487,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="49"/>
+      <c r="D239" s="53"/>
       <c r="E239" s="13" t="s">
         <v>167</v>
       </c>
@@ -5284,7 +5499,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="50"/>
+      <c r="D240" s="54"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -5374,7 +5589,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="48" t="s">
+      <c r="D246" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -5388,7 +5603,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="49"/>
+      <c r="D247" s="53"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -5400,7 +5615,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="49"/>
+      <c r="D248" s="53"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -5412,7 +5627,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="49"/>
+      <c r="D249" s="53"/>
       <c r="E249" s="13" t="s">
         <v>167</v>
       </c>
@@ -5424,7 +5639,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="50"/>
+      <c r="D250" s="54"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -5638,7 +5853,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="48" t="s">
+      <c r="D266" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -5654,7 +5869,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="49"/>
+      <c r="D267" s="53"/>
       <c r="E267" s="6" t="s">
         <v>168</v>
       </c>
@@ -5668,9 +5883,9 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="49"/>
+      <c r="D268" s="53"/>
       <c r="E268" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>87</v>
@@ -5682,7 +5897,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="49"/>
+      <c r="D269" s="53"/>
       <c r="E269" s="6" t="s">
         <v>169</v>
       </c>
@@ -5696,7 +5911,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="49"/>
+      <c r="D270" s="53"/>
       <c r="E270" s="6" t="s">
         <v>170</v>
       </c>
@@ -5710,7 +5925,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="49"/>
+      <c r="D271" s="53"/>
       <c r="E271" s="13" t="s">
         <v>180</v>
       </c>
@@ -5724,7 +5939,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="50"/>
+      <c r="D272" s="54"/>
       <c r="E272" s="13" t="s">
         <v>47</v>
       </c>
@@ -5740,7 +5955,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="48" t="s">
+      <c r="D273" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -5754,7 +5969,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="49"/>
+      <c r="D274" s="53"/>
       <c r="E274" s="6" t="s">
         <v>168</v>
       </c>
@@ -5766,9 +5981,9 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="49"/>
+      <c r="D275" s="53"/>
       <c r="E275" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F275" s="4"/>
       <c r="G275" s="4"/>
@@ -5778,7 +5993,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="49"/>
+      <c r="D276" s="53"/>
       <c r="E276" s="6" t="s">
         <v>169</v>
       </c>
@@ -5790,7 +6005,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="49"/>
+      <c r="D277" s="53"/>
       <c r="E277" s="6" t="s">
         <v>170</v>
       </c>
@@ -5802,7 +6017,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="49"/>
+      <c r="D278" s="53"/>
       <c r="E278" s="13" t="s">
         <v>180</v>
       </c>
@@ -5814,7 +6029,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="50"/>
+      <c r="D279" s="54"/>
       <c r="E279" s="13" t="s">
         <v>47</v>
       </c>
@@ -5904,7 +6119,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="48" t="s">
+      <c r="D285" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -5918,7 +6133,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="49"/>
+      <c r="D286" s="53"/>
       <c r="E286" s="6" t="s">
         <v>169</v>
       </c>
@@ -5930,7 +6145,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="49"/>
+      <c r="D287" s="53"/>
       <c r="E287" s="6" t="s">
         <v>170</v>
       </c>
@@ -5942,7 +6157,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="49"/>
+      <c r="D288" s="53"/>
       <c r="E288" s="13" t="s">
         <v>180</v>
       </c>
@@ -5954,7 +6169,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="50"/>
+      <c r="D289" s="54"/>
       <c r="E289" s="13" t="s">
         <v>171</v>
       </c>
@@ -5998,7 +6213,7 @@
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>104</v>
@@ -6094,7 +6309,7 @@
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F299" s="4"/>
       <c r="G299" s="4"/>
@@ -6168,7 +6383,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="48" t="s">
+      <c r="D305" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -6184,7 +6399,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="49"/>
+      <c r="D306" s="53"/>
       <c r="E306" s="6" t="s">
         <v>174</v>
       </c>
@@ -6198,9 +6413,9 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="49"/>
+      <c r="D307" s="53"/>
       <c r="E307" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>87</v>
@@ -6212,7 +6427,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="49"/>
+      <c r="D308" s="53"/>
       <c r="E308" s="6" t="s">
         <v>175</v>
       </c>
@@ -6226,7 +6441,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="49"/>
+      <c r="D309" s="53"/>
       <c r="E309" s="6" t="s">
         <v>176</v>
       </c>
@@ -6240,7 +6455,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="49"/>
+      <c r="D310" s="53"/>
       <c r="E310" s="45" t="s">
         <v>177</v>
       </c>
@@ -6254,7 +6469,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="50"/>
+      <c r="D311" s="54"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -6270,7 +6485,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="48" t="s">
+      <c r="D312" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -6284,7 +6499,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="49"/>
+      <c r="D313" s="53"/>
       <c r="E313" s="6" t="s">
         <v>174</v>
       </c>
@@ -6296,9 +6511,9 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="49"/>
+      <c r="D314" s="53"/>
       <c r="E314" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F314" s="4"/>
       <c r="G314" s="4"/>
@@ -6308,7 +6523,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="49"/>
+      <c r="D315" s="53"/>
       <c r="E315" s="6" t="s">
         <v>175</v>
       </c>
@@ -6320,7 +6535,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="49"/>
+      <c r="D316" s="53"/>
       <c r="E316" s="6" t="s">
         <v>176</v>
       </c>
@@ -6332,7 +6547,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="49"/>
+      <c r="D317" s="53"/>
       <c r="E317" s="45" t="s">
         <v>177</v>
       </c>
@@ -6344,7 +6559,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="50"/>
+      <c r="D318" s="54"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -6434,7 +6649,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="48" t="s">
+      <c r="D324" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -6448,7 +6663,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="49"/>
+      <c r="D325" s="53"/>
       <c r="E325" s="6" t="s">
         <v>175</v>
       </c>
@@ -6460,7 +6675,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="49"/>
+      <c r="D326" s="53"/>
       <c r="E326" s="6" t="s">
         <v>176</v>
       </c>
@@ -6472,7 +6687,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="49"/>
+      <c r="D327" s="53"/>
       <c r="E327" s="45" t="s">
         <v>177</v>
       </c>
@@ -6484,7 +6699,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="50"/>
+      <c r="D328" s="54"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -6528,7 +6743,7 @@
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>104</v>
@@ -6624,7 +6839,7 @@
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F338" s="4"/>
       <c r="G338" s="4"/>
@@ -6692,7 +6907,7 @@
     </row>
     <row r="344" spans="1:9" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="47" t="s">
+      <c r="B344" s="55" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -6708,7 +6923,7 @@
     </row>
     <row r="345" spans="1:9" s="9" customFormat="1">
       <c r="A345" s="8"/>
-      <c r="B345" s="51"/>
+      <c r="B345" s="56"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -6720,7 +6935,7 @@
     </row>
     <row r="346" spans="1:9" s="9" customFormat="1">
       <c r="A346" s="8"/>
-      <c r="B346" s="51"/>
+      <c r="B346" s="56"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -6732,7 +6947,7 @@
     </row>
     <row r="347" spans="1:9" s="9" customFormat="1">
       <c r="A347" s="8"/>
-      <c r="B347" s="51"/>
+      <c r="B347" s="56"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -6744,7 +6959,7 @@
     </row>
     <row r="348" spans="1:9" s="9" customFormat="1">
       <c r="A348" s="8"/>
-      <c r="B348" s="51"/>
+      <c r="B348" s="56"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -6756,7 +6971,7 @@
     </row>
     <row r="349" spans="1:9" s="9" customFormat="1">
       <c r="A349" s="8"/>
-      <c r="B349" s="51"/>
+      <c r="B349" s="56"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -6768,7 +6983,7 @@
     </row>
     <row r="350" spans="1:9" s="9" customFormat="1">
       <c r="A350" s="8"/>
-      <c r="B350" s="52"/>
+      <c r="B350" s="57"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -6798,7 +7013,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="48" t="s">
+      <c r="D352" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -6814,7 +7029,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="49"/>
+      <c r="D353" s="53"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -6828,7 +7043,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="49"/>
+      <c r="D354" s="53"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -6842,7 +7057,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="50"/>
+      <c r="D355" s="54"/>
       <c r="E355" s="13" t="s">
         <v>64</v>
       </c>
@@ -6858,7 +7073,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="48" t="s">
+      <c r="D356" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -6872,7 +7087,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="49"/>
+      <c r="D357" s="53"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -6884,7 +7099,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="49"/>
+      <c r="D358" s="53"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -6896,7 +7111,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="50"/>
+      <c r="D359" s="54"/>
       <c r="E359" s="13" t="s">
         <v>64</v>
       </c>
@@ -6956,7 +7171,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="48" t="s">
+      <c r="D363" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -6970,7 +7185,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="49"/>
+      <c r="D364" s="53"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -6982,7 +7197,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="50"/>
+      <c r="D365" s="54"/>
       <c r="E365" s="13" t="s">
         <v>64</v>
       </c>
@@ -7130,7 +7345,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="48" t="s">
+      <c r="D375" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -7146,7 +7361,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="49"/>
+      <c r="D376" s="53"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -7162,7 +7377,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="50"/>
+      <c r="D377" s="54"/>
       <c r="E377" s="46" t="s">
         <v>156</v>
       </c>
@@ -7176,7 +7391,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="48" t="s">
+      <c r="D378" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -7190,7 +7405,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="49"/>
+      <c r="D379" s="53"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -7202,7 +7417,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="50"/>
+      <c r="D380" s="54"/>
       <c r="E380" s="46" t="s">
         <v>156</v>
       </c>
@@ -7246,7 +7461,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="48" t="s">
+      <c r="D383" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -7260,7 +7475,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="50"/>
+      <c r="D384" s="54"/>
       <c r="E384" s="6" t="s">
         <v>160</v>
       </c>
@@ -7364,7 +7579,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="48" t="s">
+      <c r="D392" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -7380,7 +7595,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="49"/>
+      <c r="D393" s="53"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -7396,7 +7611,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="50"/>
+      <c r="D394" s="54"/>
       <c r="E394" s="46" t="s">
         <v>156</v>
       </c>
@@ -7410,7 +7625,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="48" t="s">
+      <c r="D395" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -7424,7 +7639,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="49"/>
+      <c r="D396" s="53"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -7436,7 +7651,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="50"/>
+      <c r="D397" s="54"/>
       <c r="E397" s="46" t="s">
         <v>156</v>
       </c>
@@ -7480,7 +7695,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="48" t="s">
+      <c r="D400" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -7494,7 +7709,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="50"/>
+      <c r="D401" s="54"/>
       <c r="E401" s="6" t="s">
         <v>161</v>
       </c>
@@ -7666,7 +7881,7 @@
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
       <c r="E414" s="6" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="F414" s="4"/>
       <c r="G414" s="4"/>
@@ -7683,6 +7898,9 @@
     <mergeCell ref="D30:D37"/>
     <mergeCell ref="D38:D45"/>
     <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D73:D80"/>
+    <mergeCell ref="D81:D88"/>
+    <mergeCell ref="D95:D98"/>
     <mergeCell ref="D157:D159"/>
     <mergeCell ref="D176:D178"/>
     <mergeCell ref="D179:D181"/>
@@ -7699,9 +7917,6 @@
     <mergeCell ref="D375:D377"/>
     <mergeCell ref="D378:D380"/>
     <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D73:D80"/>
-    <mergeCell ref="D81:D88"/>
-    <mergeCell ref="D95:D98"/>
     <mergeCell ref="D392:D394"/>
     <mergeCell ref="D395:D397"/>
     <mergeCell ref="D324:D328"/>
@@ -7779,7 +7994,7 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -7797,7 +8012,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="49"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -7805,14 +8020,17 @@
         <v>23</v>
       </c>
       <c r="G4" s="4"/>
+      <c r="H4" s="10" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="49"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -7821,7 +8039,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="49"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
@@ -7836,9 +8054,9 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="50"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>24</v>
@@ -7851,7 +8069,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="52" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -7864,7 +8082,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="49"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -7875,9 +8093,9 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="49"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -7886,7 +8104,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="49"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
@@ -7899,9 +8117,9 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="50"/>
+      <c r="D12" s="54"/>
       <c r="E12" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -7959,7 +8177,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -7972,9 +8190,9 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="51"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="5" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -7983,7 +8201,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="52"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="13" t="s">
         <v>134</v>
       </c>
@@ -8000,7 +8218,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>138</v>
@@ -8026,7 +8244,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -8091,7 +8309,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -8141,7 +8359,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -8156,7 +8374,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="49"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="5" t="s">
         <v>145</v>
       </c>
@@ -8169,7 +8387,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="49"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="5" t="s">
         <v>142</v>
       </c>
@@ -8182,7 +8400,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="49"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="5" t="s">
         <v>146</v>
       </c>
@@ -8197,9 +8415,9 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="49"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -8208,9 +8426,9 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="49"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -8219,7 +8437,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="49"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="5" t="s">
         <v>151</v>
       </c>
@@ -8232,9 +8450,9 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="50"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>24</v>
@@ -8249,7 +8467,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -8262,7 +8480,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="49"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="5" t="s">
         <v>145</v>
       </c>
@@ -8273,7 +8491,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="49"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="5" t="s">
         <v>143</v>
       </c>
@@ -8284,7 +8502,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="49"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="5" t="s">
         <v>146</v>
       </c>
@@ -8295,9 +8513,9 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="49"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -8306,9 +8524,9 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="49"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -8317,9 +8535,9 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="49"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -8328,9 +8546,9 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="50"/>
+      <c r="D45" s="54"/>
       <c r="E45" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
@@ -8375,7 +8593,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -8386,7 +8604,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -8410,7 +8628,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>24</v>
@@ -8425,7 +8643,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="53" t="s">
+      <c r="D52" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -8438,7 +8656,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="4" t="s">
         <v>147</v>
       </c>
@@ -8449,7 +8667,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
@@ -8460,9 +8678,9 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="52"/>
+      <c r="D55" s="57"/>
       <c r="E55" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
@@ -8529,7 +8747,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -8540,7 +8758,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -8564,7 +8782,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>88</v>
@@ -8625,7 +8843,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -8636,7 +8854,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -8647,7 +8865,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -8658,7 +8876,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -8684,7 +8902,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -8699,7 +8917,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="49"/>
+      <c r="D74" s="53"/>
       <c r="E74" s="5" t="s">
         <v>148</v>
       </c>
@@ -8712,7 +8930,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="49"/>
+      <c r="D75" s="53"/>
       <c r="E75" s="5" t="s">
         <v>153</v>
       </c>
@@ -8725,7 +8943,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="49"/>
+      <c r="D76" s="53"/>
       <c r="E76" s="5" t="s">
         <v>149</v>
       </c>
@@ -8738,9 +8956,9 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="49"/>
+      <c r="D77" s="53"/>
       <c r="E77" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -8749,9 +8967,9 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="49"/>
+      <c r="D78" s="53"/>
       <c r="E78" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -8760,7 +8978,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="49"/>
+      <c r="D79" s="53"/>
       <c r="E79" s="13" t="s">
         <v>154</v>
       </c>
@@ -8773,9 +8991,9 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="50"/>
+      <c r="D80" s="54"/>
       <c r="E80" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>24</v>
@@ -8788,7 +9006,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="48" t="s">
+      <c r="D81" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -8801,7 +9019,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="49"/>
+      <c r="D82" s="53"/>
       <c r="E82" s="5" t="s">
         <v>148</v>
       </c>
@@ -8812,7 +9030,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="49"/>
+      <c r="D83" s="53"/>
       <c r="E83" s="5" t="s">
         <v>143</v>
       </c>
@@ -8823,7 +9041,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="49"/>
+      <c r="D84" s="53"/>
       <c r="E84" s="5" t="s">
         <v>149</v>
       </c>
@@ -8834,9 +9052,9 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="49"/>
+      <c r="D85" s="53"/>
       <c r="E85" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
@@ -8847,9 +9065,9 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="49"/>
+      <c r="D86" s="53"/>
       <c r="E86" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -8858,7 +9076,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="49"/>
+      <c r="D87" s="53"/>
       <c r="E87" s="13" t="s">
         <v>154</v>
       </c>
@@ -8869,9 +9087,9 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="50"/>
+      <c r="D88" s="54"/>
       <c r="E88" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -8914,7 +9132,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
@@ -8927,7 +9145,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -8951,7 +9169,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -8964,7 +9182,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="53" t="s">
+      <c r="D95" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -8979,7 +9197,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="51"/>
+      <c r="D96" s="56"/>
       <c r="E96" s="4" t="s">
         <v>150</v>
       </c>
@@ -8990,7 +9208,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="51"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="13" t="s">
         <v>154</v>
       </c>
@@ -9001,9 +9219,9 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="52"/>
+      <c r="D98" s="57"/>
       <c r="E98" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -9070,7 +9288,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -9081,7 +9299,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -9107,7 +9325,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>88</v>
@@ -9166,7 +9384,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -9177,7 +9395,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -9199,7 +9417,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -9223,7 +9441,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="48" t="s">
+      <c r="D116" s="52" t="s">
         <v>128</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -9240,7 +9458,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="49"/>
+      <c r="D117" s="53"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -9255,7 +9473,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="50"/>
+      <c r="D118" s="54"/>
       <c r="E118" s="6" t="s">
         <v>156</v>
       </c>
@@ -9270,7 +9488,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="48" t="s">
+      <c r="D119" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -9283,7 +9501,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="49"/>
+      <c r="D120" s="53"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -9294,7 +9512,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="50"/>
+      <c r="D121" s="54"/>
       <c r="E121" s="6" t="s">
         <v>156</v>
       </c>
@@ -9424,7 +9642,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="48" t="s">
+      <c r="D131" s="52" t="s">
         <v>128</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -9441,7 +9659,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="49"/>
+      <c r="D132" s="53"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -9456,7 +9674,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="50"/>
+      <c r="D133" s="54"/>
       <c r="E133" s="6" t="s">
         <v>156</v>
       </c>
@@ -9471,7 +9689,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="48" t="s">
+      <c r="D134" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -9484,7 +9702,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="49"/>
+      <c r="D135" s="53"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -9495,7 +9713,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="50"/>
+      <c r="D136" s="54"/>
       <c r="E136" s="6" t="s">
         <v>156</v>
       </c>
@@ -9625,7 +9843,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="48" t="s">
+      <c r="D146" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -9642,7 +9860,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="49"/>
+      <c r="D147" s="53"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -9655,7 +9873,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="49"/>
+      <c r="D148" s="53"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -9666,7 +9884,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="50"/>
+      <c r="D149" s="54"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -9679,7 +9897,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="48" t="s">
+      <c r="D150" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -9692,7 +9910,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="49"/>
+      <c r="D151" s="53"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -9703,7 +9921,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="49"/>
+      <c r="D152" s="53"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -9714,7 +9932,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="50"/>
+      <c r="D153" s="54"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -9766,7 +9984,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="48" t="s">
+      <c r="D157" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -9779,7 +9997,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="49"/>
+      <c r="D158" s="53"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -9790,7 +10008,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="50"/>
+      <c r="D159" s="54"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -10011,7 +10229,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="48" t="s">
+      <c r="D176" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -10026,7 +10244,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="49"/>
+      <c r="D177" s="53"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -10039,7 +10257,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="50"/>
+      <c r="D178" s="54"/>
       <c r="E178" s="6" t="s">
         <v>157</v>
       </c>
@@ -10054,7 +10272,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="48" t="s">
+      <c r="D179" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -10067,7 +10285,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="49"/>
+      <c r="D180" s="53"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -10078,7 +10296,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="50"/>
+      <c r="D181" s="54"/>
       <c r="E181" s="6" t="s">
         <v>157</v>
       </c>
@@ -10212,7 +10430,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="48" t="s">
+      <c r="D191" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -10227,7 +10445,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="49"/>
+      <c r="D192" s="53"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -10240,7 +10458,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="49"/>
+      <c r="D193" s="53"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -10253,7 +10471,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="49"/>
+      <c r="D194" s="53"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -10266,7 +10484,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="49"/>
+      <c r="D195" s="53"/>
       <c r="E195" s="13" t="s">
         <v>48</v>
       </c>
@@ -10281,7 +10499,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="50"/>
+      <c r="D196" s="54"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -10298,7 +10516,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="48" t="s">
+      <c r="D197" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -10311,7 +10529,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="49"/>
+      <c r="D198" s="53"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -10322,7 +10540,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="49"/>
+      <c r="D199" s="53"/>
       <c r="E199" s="6" t="s">
         <v>158</v>
       </c>
@@ -10333,7 +10551,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="49"/>
+      <c r="D200" s="53"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -10344,7 +10562,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="49"/>
+      <c r="D201" s="53"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -10355,7 +10573,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="49"/>
+      <c r="D202" s="53"/>
       <c r="E202" s="13" t="s">
         <v>163</v>
       </c>
@@ -10368,7 +10586,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="50"/>
+      <c r="D203" s="54"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -10456,7 +10674,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="48" t="s">
+      <c r="D209" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -10469,7 +10687,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="49"/>
+      <c r="D210" s="53"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -10480,7 +10698,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="49"/>
+      <c r="D211" s="53"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -10491,7 +10709,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="49"/>
+      <c r="D212" s="53"/>
       <c r="E212" s="13" t="s">
         <v>163</v>
       </c>
@@ -10504,7 +10722,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="50"/>
+      <c r="D213" s="54"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -10688,7 +10906,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="48" t="s">
+      <c r="D227" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -10703,7 +10921,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="49"/>
+      <c r="D228" s="53"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -10716,7 +10934,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="49"/>
+      <c r="D229" s="53"/>
       <c r="E229" s="6" t="s">
         <v>159</v>
       </c>
@@ -10729,7 +10947,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="49"/>
+      <c r="D230" s="53"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -10742,7 +10960,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="49"/>
+      <c r="D231" s="53"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -10755,7 +10973,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="49"/>
+      <c r="D232" s="53"/>
       <c r="E232" s="13" t="s">
         <v>167</v>
       </c>
@@ -10768,7 +10986,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="50"/>
+      <c r="D233" s="54"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -10783,7 +11001,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="48" t="s">
+      <c r="D234" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -10796,7 +11014,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="49"/>
+      <c r="D235" s="53"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -10807,7 +11025,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="49"/>
+      <c r="D236" s="53"/>
       <c r="E236" s="6" t="s">
         <v>159</v>
       </c>
@@ -10818,7 +11036,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="49"/>
+      <c r="D237" s="53"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -10829,7 +11047,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="49"/>
+      <c r="D238" s="53"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -10840,7 +11058,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="49"/>
+      <c r="D239" s="53"/>
       <c r="E239" s="13" t="s">
         <v>167</v>
       </c>
@@ -10851,7 +11069,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="50"/>
+      <c r="D240" s="54"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -10935,7 +11153,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="48" t="s">
+      <c r="D246" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -10948,7 +11166,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="49"/>
+      <c r="D247" s="53"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -10959,7 +11177,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="49"/>
+      <c r="D248" s="53"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -10970,7 +11188,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="49"/>
+      <c r="D249" s="53"/>
       <c r="E249" s="13" t="s">
         <v>167</v>
       </c>
@@ -10981,7 +11199,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="50"/>
+      <c r="D250" s="54"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -11179,7 +11397,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="48" t="s">
+      <c r="D266" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -11194,7 +11412,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="49"/>
+      <c r="D267" s="53"/>
       <c r="E267" s="6" t="s">
         <v>168</v>
       </c>
@@ -11207,9 +11425,9 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="49"/>
+      <c r="D268" s="53"/>
       <c r="E268" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>87</v>
@@ -11220,7 +11438,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="49"/>
+      <c r="D269" s="53"/>
       <c r="E269" s="6" t="s">
         <v>169</v>
       </c>
@@ -11233,7 +11451,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="49"/>
+      <c r="D270" s="53"/>
       <c r="E270" s="6" t="s">
         <v>170</v>
       </c>
@@ -11246,7 +11464,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="49"/>
+      <c r="D271" s="53"/>
       <c r="E271" s="13" t="s">
         <v>180</v>
       </c>
@@ -11259,7 +11477,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="50"/>
+      <c r="D272" s="54"/>
       <c r="E272" s="13" t="s">
         <v>47</v>
       </c>
@@ -11274,7 +11492,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="48" t="s">
+      <c r="D273" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -11287,7 +11505,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="49"/>
+      <c r="D274" s="53"/>
       <c r="E274" s="6" t="s">
         <v>168</v>
       </c>
@@ -11298,9 +11516,9 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="49"/>
+      <c r="D275" s="53"/>
       <c r="E275" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F275" s="4"/>
       <c r="G275" s="4"/>
@@ -11309,7 +11527,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="49"/>
+      <c r="D276" s="53"/>
       <c r="E276" s="6" t="s">
         <v>169</v>
       </c>
@@ -11320,7 +11538,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="49"/>
+      <c r="D277" s="53"/>
       <c r="E277" s="6" t="s">
         <v>170</v>
       </c>
@@ -11331,7 +11549,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="49"/>
+      <c r="D278" s="53"/>
       <c r="E278" s="13" t="s">
         <v>180</v>
       </c>
@@ -11342,7 +11560,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="50"/>
+      <c r="D279" s="54"/>
       <c r="E279" s="13" t="s">
         <v>47</v>
       </c>
@@ -11426,7 +11644,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="48" t="s">
+      <c r="D285" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -11439,7 +11657,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="49"/>
+      <c r="D286" s="53"/>
       <c r="E286" s="6" t="s">
         <v>169</v>
       </c>
@@ -11450,7 +11668,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="49"/>
+      <c r="D287" s="53"/>
       <c r="E287" s="6" t="s">
         <v>170</v>
       </c>
@@ -11461,7 +11679,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="49"/>
+      <c r="D288" s="53"/>
       <c r="E288" s="13" t="s">
         <v>180</v>
       </c>
@@ -11472,7 +11690,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="50"/>
+      <c r="D289" s="54"/>
       <c r="E289" s="13" t="s">
         <v>171</v>
       </c>
@@ -11513,7 +11731,7 @@
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>104</v>
@@ -11602,7 +11820,7 @@
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F299" s="4"/>
       <c r="G299" s="4"/>
@@ -11670,7 +11888,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="48" t="s">
+      <c r="D305" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -11685,7 +11903,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="49"/>
+      <c r="D306" s="53"/>
       <c r="E306" s="6" t="s">
         <v>174</v>
       </c>
@@ -11698,9 +11916,9 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="49"/>
+      <c r="D307" s="53"/>
       <c r="E307" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>87</v>
@@ -11711,7 +11929,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="49"/>
+      <c r="D308" s="53"/>
       <c r="E308" s="6" t="s">
         <v>175</v>
       </c>
@@ -11724,7 +11942,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="49"/>
+      <c r="D309" s="53"/>
       <c r="E309" s="6" t="s">
         <v>176</v>
       </c>
@@ -11737,7 +11955,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="49"/>
+      <c r="D310" s="53"/>
       <c r="E310" s="45" t="s">
         <v>177</v>
       </c>
@@ -11750,7 +11968,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="50"/>
+      <c r="D311" s="54"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -11765,7 +11983,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="48" t="s">
+      <c r="D312" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -11778,7 +11996,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="49"/>
+      <c r="D313" s="53"/>
       <c r="E313" s="6" t="s">
         <v>174</v>
       </c>
@@ -11789,9 +12007,9 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="49"/>
+      <c r="D314" s="53"/>
       <c r="E314" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F314" s="4"/>
       <c r="G314" s="4"/>
@@ -11800,7 +12018,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="49"/>
+      <c r="D315" s="53"/>
       <c r="E315" s="6" t="s">
         <v>175</v>
       </c>
@@ -11811,7 +12029,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="49"/>
+      <c r="D316" s="53"/>
       <c r="E316" s="6" t="s">
         <v>176</v>
       </c>
@@ -11822,7 +12040,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="49"/>
+      <c r="D317" s="53"/>
       <c r="E317" s="45" t="s">
         <v>177</v>
       </c>
@@ -11833,7 +12051,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="50"/>
+      <c r="D318" s="54"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -11917,7 +12135,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="48" t="s">
+      <c r="D324" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -11930,7 +12148,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="49"/>
+      <c r="D325" s="53"/>
       <c r="E325" s="6" t="s">
         <v>175</v>
       </c>
@@ -11941,7 +12159,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="49"/>
+      <c r="D326" s="53"/>
       <c r="E326" s="6" t="s">
         <v>176</v>
       </c>
@@ -11952,7 +12170,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="49"/>
+      <c r="D327" s="53"/>
       <c r="E327" s="45" t="s">
         <v>177</v>
       </c>
@@ -11963,7 +12181,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="50"/>
+      <c r="D328" s="54"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -12004,7 +12222,7 @@
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>104</v>
@@ -12093,7 +12311,7 @@
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F338" s="4"/>
       <c r="G338" s="4"/>
@@ -12155,7 +12373,7 @@
     </row>
     <row r="344" spans="1:7" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="47" t="s">
+      <c r="B344" s="55" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -12170,7 +12388,7 @@
     </row>
     <row r="345" spans="1:7" s="9" customFormat="1">
       <c r="A345" s="8"/>
-      <c r="B345" s="51"/>
+      <c r="B345" s="56"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -12181,7 +12399,7 @@
     </row>
     <row r="346" spans="1:7" s="9" customFormat="1">
       <c r="A346" s="8"/>
-      <c r="B346" s="51"/>
+      <c r="B346" s="56"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -12192,7 +12410,7 @@
     </row>
     <row r="347" spans="1:7" s="9" customFormat="1">
       <c r="A347" s="8"/>
-      <c r="B347" s="51"/>
+      <c r="B347" s="56"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -12203,7 +12421,7 @@
     </row>
     <row r="348" spans="1:7" s="9" customFormat="1">
       <c r="A348" s="8"/>
-      <c r="B348" s="51"/>
+      <c r="B348" s="56"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -12214,7 +12432,7 @@
     </row>
     <row r="349" spans="1:7" s="9" customFormat="1">
       <c r="A349" s="8"/>
-      <c r="B349" s="51"/>
+      <c r="B349" s="56"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -12225,7 +12443,7 @@
     </row>
     <row r="350" spans="1:7" s="9" customFormat="1">
       <c r="A350" s="8"/>
-      <c r="B350" s="52"/>
+      <c r="B350" s="57"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -12253,7 +12471,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="48" t="s">
+      <c r="D352" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -12268,7 +12486,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="49"/>
+      <c r="D353" s="53"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -12281,7 +12499,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="49"/>
+      <c r="D354" s="53"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -12294,7 +12512,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="50"/>
+      <c r="D355" s="54"/>
       <c r="E355" s="13" t="s">
         <v>64</v>
       </c>
@@ -12309,7 +12527,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="48" t="s">
+      <c r="D356" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -12322,7 +12540,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="49"/>
+      <c r="D357" s="53"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -12333,7 +12551,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="49"/>
+      <c r="D358" s="53"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -12344,7 +12562,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="50"/>
+      <c r="D359" s="54"/>
       <c r="E359" s="13" t="s">
         <v>64</v>
       </c>
@@ -12400,7 +12618,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="48" t="s">
+      <c r="D363" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -12413,7 +12631,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="49"/>
+      <c r="D364" s="53"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -12424,7 +12642,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="50"/>
+      <c r="D365" s="54"/>
       <c r="E365" s="13" t="s">
         <v>64</v>
       </c>
@@ -12556,7 +12774,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="48" t="s">
+      <c r="D375" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -12571,7 +12789,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="49"/>
+      <c r="D376" s="53"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -12584,7 +12802,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="50"/>
+      <c r="D377" s="54"/>
       <c r="E377" s="46" t="s">
         <v>156</v>
       </c>
@@ -12597,7 +12815,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="48" t="s">
+      <c r="D378" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -12610,7 +12828,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="49"/>
+      <c r="D379" s="53"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -12621,7 +12839,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="50"/>
+      <c r="D380" s="54"/>
       <c r="E380" s="46" t="s">
         <v>156</v>
       </c>
@@ -12662,7 +12880,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="48" t="s">
+      <c r="D383" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -12675,7 +12893,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="50"/>
+      <c r="D384" s="54"/>
       <c r="E384" s="6" t="s">
         <v>160</v>
       </c>
@@ -12771,7 +12989,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="48" t="s">
+      <c r="D392" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -12786,7 +13004,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="49"/>
+      <c r="D393" s="53"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -12799,7 +13017,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="50"/>
+      <c r="D394" s="54"/>
       <c r="E394" s="46" t="s">
         <v>156</v>
       </c>
@@ -12812,7 +13030,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="48" t="s">
+      <c r="D395" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -12825,7 +13043,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="49"/>
+      <c r="D396" s="53"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -12836,7 +13054,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="50"/>
+      <c r="D397" s="54"/>
       <c r="E397" s="46" t="s">
         <v>156</v>
       </c>
@@ -12877,7 +13095,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="48" t="s">
+      <c r="D400" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -12890,7 +13108,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="50"/>
+      <c r="D401" s="54"/>
       <c r="E401" s="6" t="s">
         <v>161</v>
       </c>
@@ -13080,12 +13298,12 @@
     <mergeCell ref="D134:D136"/>
     <mergeCell ref="D146:D149"/>
     <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D150:D153"/>
     <mergeCell ref="D52:D55"/>
     <mergeCell ref="D73:D80"/>
     <mergeCell ref="D81:D88"/>
     <mergeCell ref="D95:D98"/>
     <mergeCell ref="D116:D118"/>
-    <mergeCell ref="D150:D153"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D8:D12"/>
     <mergeCell ref="D16:D18"/>
@@ -13101,15 +13319,15 @@
     <mergeCell ref="D246:D250"/>
     <mergeCell ref="D266:D272"/>
     <mergeCell ref="D273:D279"/>
+    <mergeCell ref="D383:D384"/>
+    <mergeCell ref="D392:D394"/>
+    <mergeCell ref="D395:D397"/>
+    <mergeCell ref="D400:D401"/>
     <mergeCell ref="D352:D355"/>
     <mergeCell ref="D356:D359"/>
     <mergeCell ref="D363:D365"/>
     <mergeCell ref="D375:D377"/>
     <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D392:D394"/>
-    <mergeCell ref="D395:D397"/>
-    <mergeCell ref="D400:D401"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13179,7 +13397,7 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -13197,7 +13415,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="49"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -13213,9 +13431,9 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="49"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -13224,7 +13442,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="49"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
@@ -13239,9 +13457,9 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="50"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>24</v>
@@ -13254,7 +13472,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="52" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -13267,7 +13485,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="49"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -13278,9 +13496,9 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="49"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -13289,7 +13507,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="49"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
@@ -13302,9 +13520,9 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="50"/>
+      <c r="D12" s="54"/>
       <c r="E12" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -13362,7 +13580,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -13375,9 +13593,9 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="51"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="5" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -13386,7 +13604,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="52"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="13" t="s">
         <v>134</v>
       </c>
@@ -13403,7 +13621,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>138</v>
@@ -13429,7 +13647,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -13494,7 +13712,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -13544,7 +13762,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -13559,7 +13777,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="49"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="5" t="s">
         <v>145</v>
       </c>
@@ -13572,7 +13790,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="49"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="5" t="s">
         <v>142</v>
       </c>
@@ -13585,7 +13803,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="49"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="5" t="s">
         <v>146</v>
       </c>
@@ -13600,9 +13818,9 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="49"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -13611,9 +13829,9 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="49"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -13622,7 +13840,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="49"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="5" t="s">
         <v>151</v>
       </c>
@@ -13635,9 +13853,9 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="50"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>24</v>
@@ -13652,7 +13870,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -13665,7 +13883,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="49"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="5" t="s">
         <v>145</v>
       </c>
@@ -13676,7 +13894,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="49"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="5" t="s">
         <v>143</v>
       </c>
@@ -13687,7 +13905,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="49"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="5" t="s">
         <v>146</v>
       </c>
@@ -13698,9 +13916,9 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="49"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -13709,9 +13927,9 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="49"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -13720,9 +13938,9 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="49"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -13731,9 +13949,9 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="50"/>
+      <c r="D45" s="54"/>
       <c r="E45" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
@@ -13778,7 +13996,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -13789,7 +14007,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -13813,7 +14031,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>24</v>
@@ -13828,7 +14046,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="53" t="s">
+      <c r="D52" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -13841,7 +14059,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="4" t="s">
         <v>147</v>
       </c>
@@ -13852,7 +14070,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
@@ -13863,9 +14081,9 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="52"/>
+      <c r="D55" s="57"/>
       <c r="E55" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
@@ -13932,7 +14150,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -13943,7 +14161,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -13967,7 +14185,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>88</v>
@@ -14028,7 +14246,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="5" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -14039,7 +14257,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="5" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -14050,7 +14268,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="5" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -14061,7 +14279,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -14087,7 +14305,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -14102,7 +14320,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="49"/>
+      <c r="D74" s="53"/>
       <c r="E74" s="5" t="s">
         <v>148</v>
       </c>
@@ -14115,7 +14333,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="49"/>
+      <c r="D75" s="53"/>
       <c r="E75" s="5" t="s">
         <v>153</v>
       </c>
@@ -14128,7 +14346,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="49"/>
+      <c r="D76" s="53"/>
       <c r="E76" s="5" t="s">
         <v>149</v>
       </c>
@@ -14141,9 +14359,9 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="49"/>
+      <c r="D77" s="53"/>
       <c r="E77" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -14152,9 +14370,9 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="49"/>
+      <c r="D78" s="53"/>
       <c r="E78" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -14163,7 +14381,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="49"/>
+      <c r="D79" s="53"/>
       <c r="E79" s="13" t="s">
         <v>154</v>
       </c>
@@ -14176,9 +14394,9 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="50"/>
+      <c r="D80" s="54"/>
       <c r="E80" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>24</v>
@@ -14191,7 +14409,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="48" t="s">
+      <c r="D81" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -14204,7 +14422,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="49"/>
+      <c r="D82" s="53"/>
       <c r="E82" s="5" t="s">
         <v>148</v>
       </c>
@@ -14215,7 +14433,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="49"/>
+      <c r="D83" s="53"/>
       <c r="E83" s="5" t="s">
         <v>143</v>
       </c>
@@ -14226,7 +14444,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="49"/>
+      <c r="D84" s="53"/>
       <c r="E84" s="5" t="s">
         <v>149</v>
       </c>
@@ -14237,9 +14455,9 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="49"/>
+      <c r="D85" s="53"/>
       <c r="E85" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
@@ -14250,9 +14468,9 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="49"/>
+      <c r="D86" s="53"/>
       <c r="E86" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -14261,7 +14479,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="49"/>
+      <c r="D87" s="53"/>
       <c r="E87" s="13" t="s">
         <v>154</v>
       </c>
@@ -14272,9 +14490,9 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="50"/>
+      <c r="D88" s="54"/>
       <c r="E88" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -14317,7 +14535,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
@@ -14330,7 +14548,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -14354,7 +14572,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -14367,7 +14585,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="53" t="s">
+      <c r="D95" s="58" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -14382,7 +14600,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="51"/>
+      <c r="D96" s="56"/>
       <c r="E96" s="4" t="s">
         <v>150</v>
       </c>
@@ -14393,7 +14611,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="51"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="13" t="s">
         <v>154</v>
       </c>
@@ -14404,9 +14622,9 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="52"/>
+      <c r="D98" s="57"/>
       <c r="E98" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -14473,7 +14691,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -14484,7 +14702,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -14510,7 +14728,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>88</v>
@@ -14569,7 +14787,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -14580,7 +14798,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -14602,7 +14820,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -14626,7 +14844,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="48" t="s">
+      <c r="D116" s="52" t="s">
         <v>128</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -14643,7 +14861,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="49"/>
+      <c r="D117" s="53"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -14658,7 +14876,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="50"/>
+      <c r="D118" s="54"/>
       <c r="E118" s="6" t="s">
         <v>156</v>
       </c>
@@ -14673,7 +14891,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="48" t="s">
+      <c r="D119" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -14686,7 +14904,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="49"/>
+      <c r="D120" s="53"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -14697,7 +14915,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="50"/>
+      <c r="D121" s="54"/>
       <c r="E121" s="6" t="s">
         <v>156</v>
       </c>
@@ -14827,7 +15045,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="48" t="s">
+      <c r="D131" s="52" t="s">
         <v>128</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -14844,7 +15062,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="49"/>
+      <c r="D132" s="53"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -14859,7 +15077,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="50"/>
+      <c r="D133" s="54"/>
       <c r="E133" s="6" t="s">
         <v>156</v>
       </c>
@@ -14874,7 +15092,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="48" t="s">
+      <c r="D134" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -14887,7 +15105,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="49"/>
+      <c r="D135" s="53"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -14898,7 +15116,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="50"/>
+      <c r="D136" s="54"/>
       <c r="E136" s="6" t="s">
         <v>156</v>
       </c>
@@ -15028,7 +15246,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="48" t="s">
+      <c r="D146" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -15045,7 +15263,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="49"/>
+      <c r="D147" s="53"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -15058,7 +15276,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="49"/>
+      <c r="D148" s="53"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -15069,7 +15287,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="50"/>
+      <c r="D149" s="54"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -15082,7 +15300,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="48" t="s">
+      <c r="D150" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -15095,7 +15313,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="49"/>
+      <c r="D151" s="53"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -15106,7 +15324,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="49"/>
+      <c r="D152" s="53"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -15117,7 +15335,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="50"/>
+      <c r="D153" s="54"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -15169,7 +15387,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="48" t="s">
+      <c r="D157" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -15182,7 +15400,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="49"/>
+      <c r="D158" s="53"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -15193,7 +15411,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="50"/>
+      <c r="D159" s="54"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -15414,7 +15632,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="48" t="s">
+      <c r="D176" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -15429,7 +15647,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="49"/>
+      <c r="D177" s="53"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -15442,7 +15660,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="50"/>
+      <c r="D178" s="54"/>
       <c r="E178" s="6" t="s">
         <v>157</v>
       </c>
@@ -15457,7 +15675,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="48" t="s">
+      <c r="D179" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -15470,7 +15688,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="49"/>
+      <c r="D180" s="53"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -15481,7 +15699,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="50"/>
+      <c r="D181" s="54"/>
       <c r="E181" s="6" t="s">
         <v>157</v>
       </c>
@@ -15615,7 +15833,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="48" t="s">
+      <c r="D191" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -15630,7 +15848,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="49"/>
+      <c r="D192" s="53"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -15643,7 +15861,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="49"/>
+      <c r="D193" s="53"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -15656,7 +15874,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="49"/>
+      <c r="D194" s="53"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -15669,7 +15887,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="49"/>
+      <c r="D195" s="53"/>
       <c r="E195" s="13" t="s">
         <v>48</v>
       </c>
@@ -15684,7 +15902,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="50"/>
+      <c r="D196" s="54"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -15701,7 +15919,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="48" t="s">
+      <c r="D197" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -15714,7 +15932,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="49"/>
+      <c r="D198" s="53"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -15725,7 +15943,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="49"/>
+      <c r="D199" s="53"/>
       <c r="E199" s="6" t="s">
         <v>158</v>
       </c>
@@ -15736,7 +15954,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="49"/>
+      <c r="D200" s="53"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -15747,7 +15965,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="49"/>
+      <c r="D201" s="53"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -15758,7 +15976,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="49"/>
+      <c r="D202" s="53"/>
       <c r="E202" s="13" t="s">
         <v>163</v>
       </c>
@@ -15771,7 +15989,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="50"/>
+      <c r="D203" s="54"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -15859,7 +16077,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="48" t="s">
+      <c r="D209" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -15872,7 +16090,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="49"/>
+      <c r="D210" s="53"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -15883,7 +16101,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="49"/>
+      <c r="D211" s="53"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -15894,7 +16112,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="49"/>
+      <c r="D212" s="53"/>
       <c r="E212" s="13" t="s">
         <v>163</v>
       </c>
@@ -15907,7 +16125,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="50"/>
+      <c r="D213" s="54"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -16091,7 +16309,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="48" t="s">
+      <c r="D227" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -16106,7 +16324,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="49"/>
+      <c r="D228" s="53"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -16119,7 +16337,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="49"/>
+      <c r="D229" s="53"/>
       <c r="E229" s="6" t="s">
         <v>159</v>
       </c>
@@ -16132,7 +16350,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="49"/>
+      <c r="D230" s="53"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -16145,7 +16363,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="49"/>
+      <c r="D231" s="53"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -16158,7 +16376,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="49"/>
+      <c r="D232" s="53"/>
       <c r="E232" s="13" t="s">
         <v>167</v>
       </c>
@@ -16171,7 +16389,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="50"/>
+      <c r="D233" s="54"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -16186,7 +16404,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="48" t="s">
+      <c r="D234" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -16199,7 +16417,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="49"/>
+      <c r="D235" s="53"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -16210,7 +16428,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="49"/>
+      <c r="D236" s="53"/>
       <c r="E236" s="6" t="s">
         <v>159</v>
       </c>
@@ -16221,7 +16439,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="49"/>
+      <c r="D237" s="53"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -16232,7 +16450,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="49"/>
+      <c r="D238" s="53"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -16243,7 +16461,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="49"/>
+      <c r="D239" s="53"/>
       <c r="E239" s="13" t="s">
         <v>167</v>
       </c>
@@ -16254,7 +16472,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="50"/>
+      <c r="D240" s="54"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -16338,7 +16556,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="48" t="s">
+      <c r="D246" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -16351,7 +16569,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="49"/>
+      <c r="D247" s="53"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -16362,7 +16580,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="49"/>
+      <c r="D248" s="53"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -16373,7 +16591,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="49"/>
+      <c r="D249" s="53"/>
       <c r="E249" s="13" t="s">
         <v>167</v>
       </c>
@@ -16384,7 +16602,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="50"/>
+      <c r="D250" s="54"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -16582,7 +16800,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="48" t="s">
+      <c r="D266" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -16597,7 +16815,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="49"/>
+      <c r="D267" s="53"/>
       <c r="E267" s="6" t="s">
         <v>168</v>
       </c>
@@ -16610,9 +16828,9 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="49"/>
+      <c r="D268" s="53"/>
       <c r="E268" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>87</v>
@@ -16623,7 +16841,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="49"/>
+      <c r="D269" s="53"/>
       <c r="E269" s="6" t="s">
         <v>169</v>
       </c>
@@ -16636,7 +16854,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="49"/>
+      <c r="D270" s="53"/>
       <c r="E270" s="6" t="s">
         <v>170</v>
       </c>
@@ -16649,7 +16867,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="49"/>
+      <c r="D271" s="53"/>
       <c r="E271" s="13" t="s">
         <v>180</v>
       </c>
@@ -16662,7 +16880,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="50"/>
+      <c r="D272" s="54"/>
       <c r="E272" s="13" t="s">
         <v>47</v>
       </c>
@@ -16677,7 +16895,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="48" t="s">
+      <c r="D273" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -16690,7 +16908,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="49"/>
+      <c r="D274" s="53"/>
       <c r="E274" s="6" t="s">
         <v>168</v>
       </c>
@@ -16701,9 +16919,9 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="49"/>
+      <c r="D275" s="53"/>
       <c r="E275" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F275" s="4"/>
       <c r="G275" s="4"/>
@@ -16712,7 +16930,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="49"/>
+      <c r="D276" s="53"/>
       <c r="E276" s="6" t="s">
         <v>169</v>
       </c>
@@ -16723,7 +16941,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="49"/>
+      <c r="D277" s="53"/>
       <c r="E277" s="6" t="s">
         <v>170</v>
       </c>
@@ -16734,7 +16952,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="49"/>
+      <c r="D278" s="53"/>
       <c r="E278" s="13" t="s">
         <v>180</v>
       </c>
@@ -16745,7 +16963,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="50"/>
+      <c r="D279" s="54"/>
       <c r="E279" s="13" t="s">
         <v>47</v>
       </c>
@@ -16829,7 +17047,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="48" t="s">
+      <c r="D285" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -16842,7 +17060,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="49"/>
+      <c r="D286" s="53"/>
       <c r="E286" s="6" t="s">
         <v>169</v>
       </c>
@@ -16853,7 +17071,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="49"/>
+      <c r="D287" s="53"/>
       <c r="E287" s="6" t="s">
         <v>170</v>
       </c>
@@ -16864,7 +17082,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="49"/>
+      <c r="D288" s="53"/>
       <c r="E288" s="13" t="s">
         <v>180</v>
       </c>
@@ -16875,7 +17093,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="50"/>
+      <c r="D289" s="54"/>
       <c r="E289" s="13" t="s">
         <v>171</v>
       </c>
@@ -16916,7 +17134,7 @@
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>104</v>
@@ -17005,7 +17223,7 @@
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F299" s="4"/>
       <c r="G299" s="4"/>
@@ -17073,7 +17291,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="48" t="s">
+      <c r="D305" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -17088,7 +17306,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="49"/>
+      <c r="D306" s="53"/>
       <c r="E306" s="6" t="s">
         <v>174</v>
       </c>
@@ -17101,9 +17319,9 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="49"/>
+      <c r="D307" s="53"/>
       <c r="E307" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>87</v>
@@ -17114,7 +17332,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="49"/>
+      <c r="D308" s="53"/>
       <c r="E308" s="6" t="s">
         <v>175</v>
       </c>
@@ -17127,7 +17345,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="49"/>
+      <c r="D309" s="53"/>
       <c r="E309" s="6" t="s">
         <v>176</v>
       </c>
@@ -17140,7 +17358,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="49"/>
+      <c r="D310" s="53"/>
       <c r="E310" s="45" t="s">
         <v>177</v>
       </c>
@@ -17153,7 +17371,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="50"/>
+      <c r="D311" s="54"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -17168,7 +17386,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="48" t="s">
+      <c r="D312" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -17181,7 +17399,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="49"/>
+      <c r="D313" s="53"/>
       <c r="E313" s="6" t="s">
         <v>174</v>
       </c>
@@ -17192,9 +17410,9 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="49"/>
+      <c r="D314" s="53"/>
       <c r="E314" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F314" s="4"/>
       <c r="G314" s="4"/>
@@ -17203,7 +17421,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="49"/>
+      <c r="D315" s="53"/>
       <c r="E315" s="6" t="s">
         <v>175</v>
       </c>
@@ -17214,7 +17432,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="49"/>
+      <c r="D316" s="53"/>
       <c r="E316" s="6" t="s">
         <v>176</v>
       </c>
@@ -17225,7 +17443,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="49"/>
+      <c r="D317" s="53"/>
       <c r="E317" s="45" t="s">
         <v>177</v>
       </c>
@@ -17236,7 +17454,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="50"/>
+      <c r="D318" s="54"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -17320,7 +17538,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="48" t="s">
+      <c r="D324" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -17333,7 +17551,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="49"/>
+      <c r="D325" s="53"/>
       <c r="E325" s="6" t="s">
         <v>175</v>
       </c>
@@ -17344,7 +17562,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="49"/>
+      <c r="D326" s="53"/>
       <c r="E326" s="6" t="s">
         <v>176</v>
       </c>
@@ -17355,7 +17573,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="49"/>
+      <c r="D327" s="53"/>
       <c r="E327" s="45" t="s">
         <v>177</v>
       </c>
@@ -17366,7 +17584,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="50"/>
+      <c r="D328" s="54"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -17407,7 +17625,7 @@
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>104</v>
@@ -17496,7 +17714,7 @@
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F338" s="4"/>
       <c r="G338" s="4"/>
@@ -17558,7 +17776,7 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="8"/>
-      <c r="B344" s="47" t="s">
+      <c r="B344" s="55" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -17573,7 +17791,7 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="8"/>
-      <c r="B345" s="51"/>
+      <c r="B345" s="56"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -17584,7 +17802,7 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="8"/>
-      <c r="B346" s="51"/>
+      <c r="B346" s="56"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -17595,7 +17813,7 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="8"/>
-      <c r="B347" s="51"/>
+      <c r="B347" s="56"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -17606,7 +17824,7 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="8"/>
-      <c r="B348" s="51"/>
+      <c r="B348" s="56"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -17617,7 +17835,7 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="8"/>
-      <c r="B349" s="51"/>
+      <c r="B349" s="56"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -17628,7 +17846,7 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="8"/>
-      <c r="B350" s="52"/>
+      <c r="B350" s="57"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -17656,7 +17874,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="48" t="s">
+      <c r="D352" s="52" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -17671,7 +17889,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="49"/>
+      <c r="D353" s="53"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -17684,7 +17902,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="49"/>
+      <c r="D354" s="53"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -17697,7 +17915,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="50"/>
+      <c r="D355" s="54"/>
       <c r="E355" s="13" t="s">
         <v>64</v>
       </c>
@@ -17712,7 +17930,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="48" t="s">
+      <c r="D356" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -17725,7 +17943,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="49"/>
+      <c r="D357" s="53"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -17736,7 +17954,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="49"/>
+      <c r="D358" s="53"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -17747,7 +17965,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="50"/>
+      <c r="D359" s="54"/>
       <c r="E359" s="13" t="s">
         <v>64</v>
       </c>
@@ -17803,7 +18021,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="48" t="s">
+      <c r="D363" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -17816,7 +18034,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="49"/>
+      <c r="D364" s="53"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -17827,7 +18045,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="50"/>
+      <c r="D365" s="54"/>
       <c r="E365" s="13" t="s">
         <v>64</v>
       </c>
@@ -17959,7 +18177,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="48" t="s">
+      <c r="D375" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -17974,7 +18192,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="49"/>
+      <c r="D376" s="53"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -17987,7 +18205,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="50"/>
+      <c r="D377" s="54"/>
       <c r="E377" s="46" t="s">
         <v>156</v>
       </c>
@@ -18000,7 +18218,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="48" t="s">
+      <c r="D378" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -18013,7 +18231,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="49"/>
+      <c r="D379" s="53"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -18024,7 +18242,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="50"/>
+      <c r="D380" s="54"/>
       <c r="E380" s="46" t="s">
         <v>156</v>
       </c>
@@ -18065,7 +18283,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="48" t="s">
+      <c r="D383" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -18078,7 +18296,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="50"/>
+      <c r="D384" s="54"/>
       <c r="E384" s="6" t="s">
         <v>160</v>
       </c>
@@ -18174,7 +18392,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="48" t="s">
+      <c r="D392" s="52" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -18189,7 +18407,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="49"/>
+      <c r="D393" s="53"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -18202,7 +18420,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="50"/>
+      <c r="D394" s="54"/>
       <c r="E394" s="46" t="s">
         <v>156</v>
       </c>
@@ -18215,7 +18433,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="48" t="s">
+      <c r="D395" s="52" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -18228,7 +18446,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="49"/>
+      <c r="D396" s="53"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -18239,7 +18457,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="50"/>
+      <c r="D397" s="54"/>
       <c r="E397" s="46" t="s">
         <v>156</v>
       </c>
@@ -18280,7 +18498,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="48" t="s">
+      <c r="D400" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -18293,7 +18511,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="50"/>
+      <c r="D401" s="54"/>
       <c r="E401" s="6" t="s">
         <v>161</v>
       </c>
@@ -18480,21 +18698,21 @@
     <mergeCell ref="D234:D240"/>
     <mergeCell ref="D246:D250"/>
     <mergeCell ref="D266:D272"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="D30:D37"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D73:D80"/>
+    <mergeCell ref="D81:D88"/>
     <mergeCell ref="D95:D98"/>
     <mergeCell ref="D116:D118"/>
     <mergeCell ref="D119:D121"/>
     <mergeCell ref="D131:D133"/>
     <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D30:D37"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D73:D80"/>
-    <mergeCell ref="D81:D88"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="D179:D181"/>
     <mergeCell ref="D191:D196"/>
     <mergeCell ref="D197:D203"/>
     <mergeCell ref="D150:D153"/>
@@ -18548,78 +18766,78 @@
     </row>
     <row r="2" spans="1:6" s="31" customFormat="1">
       <c r="A2" s="28" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>188</v>
+        <v>241</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="31" customFormat="1">
       <c r="A3" s="32"/>
       <c r="B3" s="33" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="32"/>
       <c r="B4" s="33" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:6" s="31" customFormat="1">
       <c r="A5" s="32"/>
       <c r="B5" s="38" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="31" customFormat="1">
       <c r="A6" s="35"/>
       <c r="B6" s="43" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="31" customFormat="1">
@@ -18627,116 +18845,116 @@
         <v>27</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>191</v>
+        <v>319</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="31" customFormat="1">
       <c r="A8" s="32"/>
       <c r="B8" s="33" t="s">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="31" customFormat="1">
       <c r="A9" s="32"/>
       <c r="B9" s="33" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:6" s="31" customFormat="1">
       <c r="A10" s="32"/>
       <c r="B10" s="33" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:6" s="31" customFormat="1">
       <c r="A11" s="32"/>
       <c r="B11" s="33" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" s="31" customFormat="1">
       <c r="A12" s="32"/>
       <c r="B12" s="33" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="E12" s="34"/>
     </row>
     <row r="13" spans="1:6" s="31" customFormat="1">
       <c r="A13" s="32"/>
       <c r="B13" s="33" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="31" customFormat="1">
       <c r="A14" s="35"/>
       <c r="B14" s="38" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="31" customFormat="1">
@@ -18744,116 +18962,116 @@
         <v>127</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="31" customFormat="1">
       <c r="A16" s="32"/>
       <c r="B16" s="33" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="31" customFormat="1">
       <c r="A17" s="32"/>
       <c r="B17" s="33" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="E17" s="34"/>
     </row>
     <row r="18" spans="1:6" s="31" customFormat="1">
       <c r="A18" s="32"/>
       <c r="B18" s="33" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:6" s="31" customFormat="1">
       <c r="A19" s="32"/>
       <c r="B19" s="33" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="E19" s="34"/>
     </row>
     <row r="20" spans="1:6" s="31" customFormat="1">
       <c r="A20" s="32"/>
       <c r="B20" s="33" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="E20" s="34"/>
     </row>
     <row r="21" spans="1:6" s="31" customFormat="1">
       <c r="A21" s="32"/>
       <c r="B21" s="38" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="31" customFormat="1">
       <c r="A22" s="35"/>
       <c r="B22" s="36" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="31" customFormat="1">
@@ -18876,13 +19094,13 @@
     <row r="24" spans="1:6" s="31" customFormat="1">
       <c r="A24" s="32"/>
       <c r="B24" s="33" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E24" s="34"/>
     </row>
@@ -18904,306 +19122,306 @@
     <row r="26" spans="1:6" s="31" customFormat="1">
       <c r="A26" s="32"/>
       <c r="B26" s="33" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="14" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="18"/>
       <c r="B29" s="26" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="E29" s="27"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="14" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
-        <v>185</v>
+        <v>271</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>185</v>
+        <v>271</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>185</v>
+        <v>271</v>
       </c>
       <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="18"/>
       <c r="B32" s="26" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="14" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>188</v>
+        <v>274</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="15"/>
       <c r="B34" s="16" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="E34" s="17"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="18"/>
       <c r="B35" s="26" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E35" s="27"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="F36" s="22" t="s">
         <v>200</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="18"/>
       <c r="B38" s="44" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="C38" s="44" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="E38" s="27"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="14" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>188</v>
+        <v>281</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="E40" s="17"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="18"/>
       <c r="B41" s="44" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="E41" s="27"/>
     </row>
     <row r="42" spans="1:6" s="31" customFormat="1">
       <c r="A42" s="28" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>188</v>
+        <v>284</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="31" customFormat="1">
       <c r="A43" s="32"/>
       <c r="B43" s="33" t="s">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="E43" s="34"/>
     </row>
     <row r="44" spans="1:6" s="31" customFormat="1">
       <c r="A44" s="32"/>
       <c r="B44" s="33" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="31" customFormat="1">
       <c r="A45" s="35"/>
       <c r="B45" s="36" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -19211,543 +19429,541 @@
         <v>44</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="15"/>
       <c r="B47" s="22" t="s">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="E47" s="17"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="15"/>
-      <c r="B48" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="42" t="s">
-        <v>186</v>
-      </c>
+      <c r="B48" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="E48" s="17"/>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="15"/>
-      <c r="B49" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>187</v>
+      <c r="B49" s="41" t="s">
+        <v>291</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>291</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>291</v>
+      </c>
+      <c r="E49" s="42" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="15"/>
       <c r="B50" s="22" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="18"/>
-      <c r="B51" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>204</v>
+      <c r="A51" s="15"/>
+      <c r="B51" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D52" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>233</v>
+      <c r="A52" s="18"/>
+      <c r="B52" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="15"/>
-      <c r="B53" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="E53" s="17"/>
+      <c r="A53" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="15"/>
       <c r="B54" s="22" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="E54" s="17"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="15"/>
-      <c r="B55" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="E55" s="42" t="s">
-        <v>186</v>
-      </c>
+      <c r="B55" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="15"/>
-      <c r="B56" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>187</v>
+      <c r="B56" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="E56" s="42" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="15"/>
       <c r="B57" s="22" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="18"/>
-      <c r="B58" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>204</v>
+      <c r="A58" s="15"/>
+      <c r="B58" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D59" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E59" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>212</v>
+      <c r="A59" s="18"/>
+      <c r="B59" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="15"/>
-      <c r="B60" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="E60" s="17"/>
+      <c r="A60" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="15"/>
       <c r="B61" s="22" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="E61" s="17"/>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="15"/>
-      <c r="B62" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="E62" s="42" t="s">
-        <v>186</v>
-      </c>
+      <c r="B62" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="E62" s="17"/>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="15"/>
       <c r="B63" s="41" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="C63" s="41" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="D63" s="41" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="E63" s="42" t="s">
-        <v>209</v>
+        <v>307</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="15"/>
-      <c r="B64" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="C64" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="E64" s="23" t="s">
-        <v>203</v>
+      <c r="B64" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="C64" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="E64" s="42" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="18"/>
-      <c r="B65" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="D65" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="E65" s="27" t="s">
-        <v>204</v>
+      <c r="A65" s="15"/>
+      <c r="B65" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C66" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>212</v>
+      <c r="A66" s="18"/>
+      <c r="B66" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="D66" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="15"/>
-      <c r="B67" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C67" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="E67" s="17"/>
+      <c r="A67" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="F67" s="22" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="15"/>
       <c r="B68" s="22" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="E68" s="17"/>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="15"/>
       <c r="B69" s="22" t="s">
-        <v>186</v>
+        <v>314</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>186</v>
+        <v>314</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" s="23" t="s">
-        <v>186</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="E69" s="17"/>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="15"/>
       <c r="B70" s="22" t="s">
-        <v>187</v>
+        <v>315</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>187</v>
+        <v>315</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>187</v>
+        <v>315</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>187</v>
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="15"/>
       <c r="B71" s="22" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="18"/>
-      <c r="B72" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C72" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="D72" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="E72" s="27" t="s">
-        <v>204</v>
+      <c r="A72" s="15"/>
+      <c r="B72" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="E72" s="23" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="18"/>
+      <c r="B73" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="D73" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B73" s="60" t="s">
+      <c r="B74" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="61"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="15"/>
-      <c r="B74" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="C74" s="59"/>
-      <c r="D74" s="59"/>
+      <c r="C74" s="61"/>
+      <c r="D74" s="61"/>
       <c r="E74" s="62"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="15"/>
       <c r="B75" s="59" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="C75" s="59"/>
       <c r="D75" s="59"/>
-      <c r="E75" s="62"/>
+      <c r="E75" s="60"/>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="15"/>
       <c r="B76" s="59" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="C76" s="59"/>
       <c r="D76" s="59"/>
-      <c r="E76" s="62"/>
+      <c r="E76" s="60"/>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="15"/>
       <c r="B77" s="59" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C77" s="59"/>
       <c r="D77" s="59"/>
-      <c r="E77" s="62"/>
+      <c r="E77" s="60"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="15"/>
       <c r="B78" s="59" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="C78" s="59"/>
       <c r="D78" s="59"/>
-      <c r="E78" s="62"/>
+      <c r="E78" s="60"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="18"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="59" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C79" s="59"/>
       <c r="D79" s="59"/>
-      <c r="E79" s="62"/>
+      <c r="E79" s="60"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="B80" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="C80" s="60"/>
-      <c r="D80" s="60"/>
-      <c r="E80" s="61"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="59" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="60"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="15"/>
-      <c r="B81" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
+      <c r="A81" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B81" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" s="61"/>
+      <c r="D81" s="61"/>
       <c r="E81" s="62"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="15"/>
       <c r="B82" s="59" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="C82" s="59"/>
       <c r="D82" s="59"/>
-      <c r="E82" s="62"/>
+      <c r="E82" s="60"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="15"/>
       <c r="B83" s="59" t="s">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="C83" s="59"/>
       <c r="D83" s="59"/>
-      <c r="E83" s="62"/>
+      <c r="E83" s="60"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="15"/>
-      <c r="B84" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="C84" s="59"/>
-      <c r="D84" s="59"/>
-      <c r="E84" s="62"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="63"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="64"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="18"/>
-      <c r="B85" s="63" t="s">
-        <v>256</v>
-      </c>
-      <c r="C85" s="63"/>
-      <c r="D85" s="63"/>
-      <c r="E85" s="64"/>
+      <c r="A85" t="s">
+        <v>322</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B79:E79"/>
+  <mergeCells count="11">
     <mergeCell ref="B80:E80"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B84:E84"/>
     <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B79:E79"/>
     <mergeCell ref="B74:E74"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B76:E76"/>
@@ -19790,49 +20006,49 @@
     </row>
     <row r="2" spans="1:6" s="31" customFormat="1">
       <c r="A2" s="28" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="31" customFormat="1">
       <c r="A3" s="32"/>
       <c r="B3" s="38" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="35"/>
       <c r="B4" s="43" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="31" customFormat="1">
@@ -19840,64 +20056,64 @@
         <v>27</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="31" customFormat="1">
       <c r="A6" s="32"/>
       <c r="B6" s="33" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="31" customFormat="1">
       <c r="A7" s="32"/>
       <c r="B7" s="33" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="31" customFormat="1">
       <c r="A8" s="35"/>
       <c r="B8" s="38" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="31" customFormat="1">
@@ -19905,64 +20121,64 @@
         <v>127</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="31" customFormat="1">
       <c r="A10" s="32"/>
       <c r="B10" s="33" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="31" customFormat="1">
       <c r="A11" s="32"/>
       <c r="B11" s="38" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="31" customFormat="1">
       <c r="A12" s="35"/>
       <c r="B12" s="36" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="31" customFormat="1">
@@ -19970,182 +20186,182 @@
         <v>60</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="31" customFormat="1">
       <c r="A14" s="32"/>
       <c r="B14" s="38" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="31" customFormat="1">
       <c r="A15" s="32"/>
-      <c r="B15" s="56" t="s">
-        <v>210</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>210</v>
+      <c r="B15" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="14" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="14" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F17" s="22"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="14" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F18" s="22"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="14" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F19" s="22"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="14" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F20" s="22"/>
     </row>
     <row r="21" spans="1:6" s="31" customFormat="1">
       <c r="A21" s="28" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="31" customFormat="1">
       <c r="A22" s="32"/>
       <c r="B22" s="38" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="31" customFormat="1">
       <c r="A23" s="35"/>
       <c r="B23" s="36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20153,334 +20369,334 @@
         <v>44</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F24" s="22"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="15"/>
-      <c r="B25" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="D25" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="E25" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="F25" s="54" t="s">
-        <v>242</v>
+      <c r="B25" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="15"/>
       <c r="B26" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="18"/>
       <c r="B27" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="14" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F28" s="22"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="15"/>
       <c r="B29" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="15"/>
       <c r="B30" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="F30" s="54" t="s">
-        <v>243</v>
+        <v>184</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="18"/>
       <c r="B31" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F32" s="22"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="15"/>
       <c r="B33" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="15"/>
       <c r="B34" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="18"/>
       <c r="B35" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="14" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F36" s="22"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="15"/>
       <c r="B37" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="15"/>
       <c r="B38" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="18"/>
       <c r="B39" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="60"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="62"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="15"/>
       <c r="B41" s="59" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C41" s="59"/>
       <c r="D41" s="59"/>
-      <c r="E41" s="62"/>
+      <c r="E41" s="60"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="15"/>
       <c r="B42" s="59" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C42" s="59"/>
       <c r="D42" s="59"/>
-      <c r="E42" s="62"/>
+      <c r="E42" s="60"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="15"/>
       <c r="B43" s="59" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="C43" s="59"/>
       <c r="D43" s="59"/>
-      <c r="E43" s="62"/>
+      <c r="E43" s="60"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="15"/>
       <c r="B44" s="59" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="C44" s="59"/>
       <c r="D44" s="59"/>
-      <c r="E44" s="62"/>
+      <c r="E44" s="60"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="15"/>
       <c r="B45" s="59" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="59"/>
-      <c r="E45" s="62"/>
+      <c r="E45" s="60"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="18"/>
       <c r="B46" s="59" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C46" s="59"/>
       <c r="D46" s="59"/>
-      <c r="E46" s="62"/>
+      <c r="E46" s="60"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="B47" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="61"/>
+        <v>228</v>
+      </c>
+      <c r="B47" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" s="61"/>
+      <c r="D47" s="61"/>
+      <c r="E47" s="62"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="15"/>
@@ -20489,21 +20705,21 @@
       </c>
       <c r="C48" s="59"/>
       <c r="D48" s="59"/>
-      <c r="E48" s="62"/>
+      <c r="E48" s="60"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="15"/>
       <c r="B49" s="59" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="59"/>
-      <c r="E49" s="62"/>
+      <c r="E49" s="60"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="18"/>
       <c r="B50" s="63" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C50" s="63"/>
       <c r="D50" s="63"/>

--- a/internal_doc/05.测试设计/可靠性测试/基本操作故障测试.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/基本操作故障测试.xlsx
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="326">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1302,6 +1302,10 @@
   </si>
   <si>
     <t>时间提前，备节点主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w=2时两个备节点CPU耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1665,6 +1669,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1674,12 +1679,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1700,7 +1705,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1708,74 +1712,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1787,7 +1723,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2123,13 +2059,13 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="52" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="4"/>
@@ -2139,7 +2075,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="53"/>
+      <c r="D4" s="54"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2153,7 +2089,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="54"/>
       <c r="E5" s="5" t="s">
         <v>211</v>
       </c>
@@ -2165,7 +2101,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="53"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
@@ -2183,7 +2119,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="54"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="13" t="s">
         <v>207</v>
       </c>
@@ -2199,7 +2135,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="53" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -2215,7 +2151,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -2229,7 +2165,7 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="54"/>
       <c r="E10" s="5" t="s">
         <v>211</v>
       </c>
@@ -2241,7 +2177,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2257,7 +2193,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="54"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="13" t="s">
         <v>207</v>
       </c>
@@ -2327,7 +2263,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -2343,7 +2279,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="56"/>
+      <c r="D17" s="57"/>
       <c r="E17" s="5" t="s">
         <v>208</v>
       </c>
@@ -2355,7 +2291,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="57"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="13" t="s">
         <v>134</v>
       </c>
@@ -2537,7 +2473,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -2553,7 +2489,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="54"/>
       <c r="E31" s="5" t="s">
         <v>145</v>
       </c>
@@ -2567,7 +2503,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="54"/>
       <c r="E32" s="5" t="s">
         <v>142</v>
       </c>
@@ -2581,7 +2517,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="54"/>
       <c r="E33" s="5" t="s">
         <v>146</v>
       </c>
@@ -2599,7 +2535,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="54"/>
       <c r="E34" s="5" t="s">
         <v>213</v>
       </c>
@@ -2611,7 +2547,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="5" t="s">
         <v>214</v>
       </c>
@@ -2623,7 +2559,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="54"/>
       <c r="E36" s="5" t="s">
         <v>151</v>
       </c>
@@ -2637,7 +2573,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="54"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="13" t="s">
         <v>210</v>
       </c>
@@ -2655,7 +2591,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -2671,7 +2607,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="54"/>
       <c r="E39" s="5" t="s">
         <v>145</v>
       </c>
@@ -2685,7 +2621,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="54"/>
       <c r="E40" s="5" t="s">
         <v>143</v>
       </c>
@@ -2699,7 +2635,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="5" t="s">
         <v>146</v>
       </c>
@@ -2713,7 +2649,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="54"/>
       <c r="E42" s="5" t="s">
         <v>213</v>
       </c>
@@ -2725,7 +2661,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="5" t="s">
         <v>214</v>
       </c>
@@ -2737,7 +2673,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="54"/>
       <c r="E44" s="5" t="s">
         <v>209</v>
       </c>
@@ -2749,7 +2685,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="54"/>
+      <c r="D45" s="55"/>
       <c r="E45" s="13" t="s">
         <v>210</v>
       </c>
@@ -2857,7 +2793,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -2873,7 +2809,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="56"/>
+      <c r="D53" s="57"/>
       <c r="E53" s="4" t="s">
         <v>147</v>
       </c>
@@ -2887,7 +2823,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="56"/>
+      <c r="D54" s="57"/>
       <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
@@ -2899,7 +2835,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="57"/>
+      <c r="D55" s="58"/>
       <c r="E55" s="13" t="s">
         <v>210</v>
       </c>
@@ -3157,7 +3093,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="52" t="s">
+      <c r="D73" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -3173,7 +3109,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="53"/>
+      <c r="D74" s="54"/>
       <c r="E74" s="5" t="s">
         <v>148</v>
       </c>
@@ -3187,7 +3123,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="53"/>
+      <c r="D75" s="54"/>
       <c r="E75" s="5" t="s">
         <v>153</v>
       </c>
@@ -3201,7 +3137,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="53"/>
+      <c r="D76" s="54"/>
       <c r="E76" s="5" t="s">
         <v>149</v>
       </c>
@@ -3215,7 +3151,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="53"/>
+      <c r="D77" s="54"/>
       <c r="E77" s="5" t="s">
         <v>215</v>
       </c>
@@ -3227,7 +3163,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="53"/>
+      <c r="D78" s="54"/>
       <c r="E78" s="5" t="s">
         <v>216</v>
       </c>
@@ -3239,7 +3175,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="53"/>
+      <c r="D79" s="54"/>
       <c r="E79" s="13" t="s">
         <v>154</v>
       </c>
@@ -3253,7 +3189,7 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="54"/>
+      <c r="D80" s="55"/>
       <c r="E80" s="5" t="s">
         <v>217</v>
       </c>
@@ -3269,7 +3205,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="52" t="s">
+      <c r="D81" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -3283,7 +3219,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="53"/>
+      <c r="D82" s="54"/>
       <c r="E82" s="5" t="s">
         <v>148</v>
       </c>
@@ -3295,7 +3231,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="53"/>
+      <c r="D83" s="54"/>
       <c r="E83" s="5" t="s">
         <v>143</v>
       </c>
@@ -3307,7 +3243,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="53"/>
+      <c r="D84" s="54"/>
       <c r="E84" s="5" t="s">
         <v>149</v>
       </c>
@@ -3319,7 +3255,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="53"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="5" t="s">
         <v>215</v>
       </c>
@@ -3333,7 +3269,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="53"/>
+      <c r="D86" s="54"/>
       <c r="E86" s="5" t="s">
         <v>216</v>
       </c>
@@ -3345,7 +3281,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="53"/>
+      <c r="D87" s="54"/>
       <c r="E87" s="13" t="s">
         <v>154</v>
       </c>
@@ -3357,7 +3293,7 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="54"/>
+      <c r="D88" s="55"/>
       <c r="E88" s="5" t="s">
         <v>217</v>
       </c>
@@ -3459,7 +3395,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="58" t="s">
+      <c r="D95" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -3475,7 +3411,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="56"/>
+      <c r="D96" s="57"/>
       <c r="E96" s="4" t="s">
         <v>150</v>
       </c>
@@ -3487,7 +3423,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="56"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="13" t="s">
         <v>154</v>
       </c>
@@ -3499,7 +3435,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="57"/>
+      <c r="D98" s="58"/>
       <c r="E98" s="5" t="s">
         <v>217</v>
       </c>
@@ -3739,7 +3675,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="52" t="s">
+      <c r="D116" s="53" t="s">
         <v>128</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -3759,7 +3695,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="53"/>
+      <c r="D117" s="54"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -3777,7 +3713,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="54"/>
+      <c r="D118" s="55"/>
       <c r="E118" s="6" t="s">
         <v>156</v>
       </c>
@@ -3793,7 +3729,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="52" t="s">
+      <c r="D119" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -3807,7 +3743,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="53"/>
+      <c r="D120" s="54"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -3819,7 +3755,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="54"/>
+      <c r="D121" s="55"/>
       <c r="E121" s="6" t="s">
         <v>156</v>
       </c>
@@ -3959,7 +3895,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="52" t="s">
+      <c r="D131" s="53" t="s">
         <v>128</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -3977,7 +3913,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="53"/>
+      <c r="D132" s="54"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -3993,7 +3929,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="54"/>
+      <c r="D133" s="55"/>
       <c r="E133" s="6" t="s">
         <v>156</v>
       </c>
@@ -4009,7 +3945,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="52" t="s">
+      <c r="D134" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -4023,7 +3959,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="53"/>
+      <c r="D135" s="54"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -4035,7 +3971,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="54"/>
+      <c r="D136" s="55"/>
       <c r="E136" s="6" t="s">
         <v>156</v>
       </c>
@@ -4175,7 +4111,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="52" t="s">
+      <c r="D146" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -4195,7 +4131,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="53"/>
+      <c r="D147" s="54"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -4211,7 +4147,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="54"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -4223,7 +4159,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="54"/>
+      <c r="D149" s="55"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -4237,7 +4173,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="52" t="s">
+      <c r="D150" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -4251,7 +4187,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="53"/>
+      <c r="D151" s="54"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -4263,7 +4199,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="53"/>
+      <c r="D152" s="54"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -4275,7 +4211,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="54"/>
+      <c r="D153" s="55"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -4331,7 +4267,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="52" t="s">
+      <c r="D157" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -4345,7 +4281,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="53"/>
+      <c r="D158" s="54"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -4357,7 +4293,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="54"/>
+      <c r="D159" s="55"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -4595,7 +4531,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="52" t="s">
+      <c r="D176" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -4611,7 +4547,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="53"/>
+      <c r="D177" s="54"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -4625,7 +4561,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="54"/>
+      <c r="D178" s="55"/>
       <c r="E178" s="6" t="s">
         <v>157</v>
       </c>
@@ -4641,7 +4577,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="52" t="s">
+      <c r="D179" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -4655,7 +4591,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="53"/>
+      <c r="D180" s="54"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -4667,7 +4603,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="54"/>
+      <c r="D181" s="55"/>
       <c r="E181" s="6" t="s">
         <v>157</v>
       </c>
@@ -4811,7 +4747,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="52" t="s">
+      <c r="D191" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -4827,7 +4763,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="53"/>
+      <c r="D192" s="54"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -4841,7 +4777,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="53"/>
+      <c r="D193" s="54"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -4855,7 +4791,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="53"/>
+      <c r="D194" s="54"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -4869,7 +4805,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="53"/>
+      <c r="D195" s="54"/>
       <c r="E195" s="13" t="s">
         <v>48</v>
       </c>
@@ -4885,7 +4821,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="54"/>
+      <c r="D196" s="55"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -4903,7 +4839,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="52" t="s">
+      <c r="D197" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -4917,7 +4853,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="53"/>
+      <c r="D198" s="54"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -4929,7 +4865,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="53"/>
+      <c r="D199" s="54"/>
       <c r="E199" s="6" t="s">
         <v>158</v>
       </c>
@@ -4941,7 +4877,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="53"/>
+      <c r="D200" s="54"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -4953,7 +4889,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="53"/>
+      <c r="D201" s="54"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -4965,7 +4901,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="53"/>
+      <c r="D202" s="54"/>
       <c r="E202" s="13" t="s">
         <v>163</v>
       </c>
@@ -4979,7 +4915,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="54"/>
+      <c r="D203" s="55"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -5073,7 +5009,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="52" t="s">
+      <c r="D209" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -5087,7 +5023,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="53"/>
+      <c r="D210" s="54"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -5099,7 +5035,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="53"/>
+      <c r="D211" s="54"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -5111,7 +5047,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="53"/>
+      <c r="D212" s="54"/>
       <c r="E212" s="13" t="s">
         <v>163</v>
       </c>
@@ -5125,7 +5061,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="54"/>
+      <c r="D213" s="55"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -5323,7 +5259,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="52" t="s">
+      <c r="D227" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -5339,7 +5275,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="53"/>
+      <c r="D228" s="54"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -5353,7 +5289,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="53"/>
+      <c r="D229" s="54"/>
       <c r="E229" s="6" t="s">
         <v>159</v>
       </c>
@@ -5367,7 +5303,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="53"/>
+      <c r="D230" s="54"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -5381,7 +5317,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="53"/>
+      <c r="D231" s="54"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -5395,7 +5331,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="53"/>
+      <c r="D232" s="54"/>
       <c r="E232" s="13" t="s">
         <v>167</v>
       </c>
@@ -5409,7 +5345,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="54"/>
+      <c r="D233" s="55"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -5425,7 +5361,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="52" t="s">
+      <c r="D234" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -5439,7 +5375,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="53"/>
+      <c r="D235" s="54"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -5451,7 +5387,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="53"/>
+      <c r="D236" s="54"/>
       <c r="E236" s="6" t="s">
         <v>159</v>
       </c>
@@ -5463,7 +5399,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="53"/>
+      <c r="D237" s="54"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -5475,7 +5411,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="53"/>
+      <c r="D238" s="54"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -5487,7 +5423,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="53"/>
+      <c r="D239" s="54"/>
       <c r="E239" s="13" t="s">
         <v>167</v>
       </c>
@@ -5499,7 +5435,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="54"/>
+      <c r="D240" s="55"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -5589,7 +5525,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="52" t="s">
+      <c r="D246" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -5603,7 +5539,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="53"/>
+      <c r="D247" s="54"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -5615,7 +5551,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="53"/>
+      <c r="D248" s="54"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -5627,7 +5563,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="53"/>
+      <c r="D249" s="54"/>
       <c r="E249" s="13" t="s">
         <v>167</v>
       </c>
@@ -5639,7 +5575,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="54"/>
+      <c r="D250" s="55"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -5853,7 +5789,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="52" t="s">
+      <c r="D266" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -5869,7 +5805,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="53"/>
+      <c r="D267" s="54"/>
       <c r="E267" s="6" t="s">
         <v>168</v>
       </c>
@@ -5883,7 +5819,7 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="53"/>
+      <c r="D268" s="54"/>
       <c r="E268" s="6" t="s">
         <v>202</v>
       </c>
@@ -5897,7 +5833,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="53"/>
+      <c r="D269" s="54"/>
       <c r="E269" s="6" t="s">
         <v>169</v>
       </c>
@@ -5911,7 +5847,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="53"/>
+      <c r="D270" s="54"/>
       <c r="E270" s="6" t="s">
         <v>170</v>
       </c>
@@ -5925,7 +5861,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="53"/>
+      <c r="D271" s="54"/>
       <c r="E271" s="13" t="s">
         <v>180</v>
       </c>
@@ -5939,7 +5875,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="54"/>
+      <c r="D272" s="55"/>
       <c r="E272" s="13" t="s">
         <v>47</v>
       </c>
@@ -5955,7 +5891,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="52" t="s">
+      <c r="D273" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -5969,7 +5905,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="53"/>
+      <c r="D274" s="54"/>
       <c r="E274" s="6" t="s">
         <v>168</v>
       </c>
@@ -5981,7 +5917,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="53"/>
+      <c r="D275" s="54"/>
       <c r="E275" s="6" t="s">
         <v>202</v>
       </c>
@@ -5993,7 +5929,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="53"/>
+      <c r="D276" s="54"/>
       <c r="E276" s="6" t="s">
         <v>169</v>
       </c>
@@ -6005,7 +5941,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="53"/>
+      <c r="D277" s="54"/>
       <c r="E277" s="6" t="s">
         <v>170</v>
       </c>
@@ -6017,7 +5953,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="53"/>
+      <c r="D278" s="54"/>
       <c r="E278" s="13" t="s">
         <v>180</v>
       </c>
@@ -6029,7 +5965,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="54"/>
+      <c r="D279" s="55"/>
       <c r="E279" s="13" t="s">
         <v>47</v>
       </c>
@@ -6119,7 +6055,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="52" t="s">
+      <c r="D285" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -6133,7 +6069,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="53"/>
+      <c r="D286" s="54"/>
       <c r="E286" s="6" t="s">
         <v>169</v>
       </c>
@@ -6145,7 +6081,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="53"/>
+      <c r="D287" s="54"/>
       <c r="E287" s="6" t="s">
         <v>170</v>
       </c>
@@ -6157,7 +6093,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="53"/>
+      <c r="D288" s="54"/>
       <c r="E288" s="13" t="s">
         <v>180</v>
       </c>
@@ -6169,7 +6105,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="54"/>
+      <c r="D289" s="55"/>
       <c r="E289" s="13" t="s">
         <v>171</v>
       </c>
@@ -6383,7 +6319,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="52" t="s">
+      <c r="D305" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -6399,7 +6335,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="53"/>
+      <c r="D306" s="54"/>
       <c r="E306" s="6" t="s">
         <v>174</v>
       </c>
@@ -6413,7 +6349,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="53"/>
+      <c r="D307" s="54"/>
       <c r="E307" s="6" t="s">
         <v>203</v>
       </c>
@@ -6427,7 +6363,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="53"/>
+      <c r="D308" s="54"/>
       <c r="E308" s="6" t="s">
         <v>175</v>
       </c>
@@ -6441,7 +6377,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="53"/>
+      <c r="D309" s="54"/>
       <c r="E309" s="6" t="s">
         <v>176</v>
       </c>
@@ -6455,7 +6391,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="53"/>
+      <c r="D310" s="54"/>
       <c r="E310" s="45" t="s">
         <v>177</v>
       </c>
@@ -6469,7 +6405,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="54"/>
+      <c r="D311" s="55"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -6485,7 +6421,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="52" t="s">
+      <c r="D312" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -6499,7 +6435,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="53"/>
+      <c r="D313" s="54"/>
       <c r="E313" s="6" t="s">
         <v>174</v>
       </c>
@@ -6511,7 +6447,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="53"/>
+      <c r="D314" s="54"/>
       <c r="E314" s="6" t="s">
         <v>203</v>
       </c>
@@ -6523,7 +6459,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="53"/>
+      <c r="D315" s="54"/>
       <c r="E315" s="6" t="s">
         <v>175</v>
       </c>
@@ -6535,7 +6471,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="53"/>
+      <c r="D316" s="54"/>
       <c r="E316" s="6" t="s">
         <v>176</v>
       </c>
@@ -6547,7 +6483,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="53"/>
+      <c r="D317" s="54"/>
       <c r="E317" s="45" t="s">
         <v>177</v>
       </c>
@@ -6559,7 +6495,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="54"/>
+      <c r="D318" s="55"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -6649,7 +6585,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="52" t="s">
+      <c r="D324" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -6663,7 +6599,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="53"/>
+      <c r="D325" s="54"/>
       <c r="E325" s="6" t="s">
         <v>175</v>
       </c>
@@ -6675,7 +6611,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="53"/>
+      <c r="D326" s="54"/>
       <c r="E326" s="6" t="s">
         <v>176</v>
       </c>
@@ -6687,7 +6623,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="53"/>
+      <c r="D327" s="54"/>
       <c r="E327" s="45" t="s">
         <v>177</v>
       </c>
@@ -6699,7 +6635,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="54"/>
+      <c r="D328" s="55"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -6907,7 +6843,7 @@
     </row>
     <row r="344" spans="1:9" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="55" t="s">
+      <c r="B344" s="59" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -6923,7 +6859,7 @@
     </row>
     <row r="345" spans="1:9" s="9" customFormat="1">
       <c r="A345" s="8"/>
-      <c r="B345" s="56"/>
+      <c r="B345" s="57"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -6935,7 +6871,7 @@
     </row>
     <row r="346" spans="1:9" s="9" customFormat="1">
       <c r="A346" s="8"/>
-      <c r="B346" s="56"/>
+      <c r="B346" s="57"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -6947,7 +6883,7 @@
     </row>
     <row r="347" spans="1:9" s="9" customFormat="1">
       <c r="A347" s="8"/>
-      <c r="B347" s="56"/>
+      <c r="B347" s="57"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -6959,7 +6895,7 @@
     </row>
     <row r="348" spans="1:9" s="9" customFormat="1">
       <c r="A348" s="8"/>
-      <c r="B348" s="56"/>
+      <c r="B348" s="57"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -6971,7 +6907,7 @@
     </row>
     <row r="349" spans="1:9" s="9" customFormat="1">
       <c r="A349" s="8"/>
-      <c r="B349" s="56"/>
+      <c r="B349" s="57"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -6983,7 +6919,7 @@
     </row>
     <row r="350" spans="1:9" s="9" customFormat="1">
       <c r="A350" s="8"/>
-      <c r="B350" s="57"/>
+      <c r="B350" s="58"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -7013,7 +6949,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="52" t="s">
+      <c r="D352" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -7029,7 +6965,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="53"/>
+      <c r="D353" s="54"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -7043,7 +6979,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="53"/>
+      <c r="D354" s="54"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -7057,7 +6993,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="54"/>
+      <c r="D355" s="55"/>
       <c r="E355" s="13" t="s">
         <v>64</v>
       </c>
@@ -7073,7 +7009,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="52" t="s">
+      <c r="D356" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -7087,7 +7023,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="53"/>
+      <c r="D357" s="54"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -7099,7 +7035,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="53"/>
+      <c r="D358" s="54"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -7111,7 +7047,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="54"/>
+      <c r="D359" s="55"/>
       <c r="E359" s="13" t="s">
         <v>64</v>
       </c>
@@ -7171,7 +7107,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="52" t="s">
+      <c r="D363" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -7185,7 +7121,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="53"/>
+      <c r="D364" s="54"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -7197,7 +7133,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="54"/>
+      <c r="D365" s="55"/>
       <c r="E365" s="13" t="s">
         <v>64</v>
       </c>
@@ -7345,7 +7281,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="52" t="s">
+      <c r="D375" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -7361,7 +7297,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="53"/>
+      <c r="D376" s="54"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -7377,7 +7313,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="54"/>
+      <c r="D377" s="55"/>
       <c r="E377" s="46" t="s">
         <v>156</v>
       </c>
@@ -7391,7 +7327,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="52" t="s">
+      <c r="D378" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -7405,7 +7341,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="53"/>
+      <c r="D379" s="54"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -7417,7 +7353,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="54"/>
+      <c r="D380" s="55"/>
       <c r="E380" s="46" t="s">
         <v>156</v>
       </c>
@@ -7461,7 +7397,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="52" t="s">
+      <c r="D383" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -7475,7 +7411,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="54"/>
+      <c r="D384" s="55"/>
       <c r="E384" s="6" t="s">
         <v>160</v>
       </c>
@@ -7579,7 +7515,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="52" t="s">
+      <c r="D392" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -7595,7 +7531,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="53"/>
+      <c r="D393" s="54"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -7611,7 +7547,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="54"/>
+      <c r="D394" s="55"/>
       <c r="E394" s="46" t="s">
         <v>156</v>
       </c>
@@ -7625,7 +7561,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="52" t="s">
+      <c r="D395" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -7639,7 +7575,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="53"/>
+      <c r="D396" s="54"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -7651,7 +7587,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="54"/>
+      <c r="D397" s="55"/>
       <c r="E397" s="46" t="s">
         <v>156</v>
       </c>
@@ -7695,7 +7631,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="52" t="s">
+      <c r="D400" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -7709,7 +7645,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="54"/>
+      <c r="D401" s="55"/>
       <c r="E401" s="6" t="s">
         <v>161</v>
       </c>
@@ -7890,6 +7826,35 @@
   </sheetData>
   <autoFilter ref="A1:G414"/>
   <mergeCells count="40">
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D209:D213"/>
+    <mergeCell ref="D191:D196"/>
+    <mergeCell ref="D227:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="D266:D272"/>
+    <mergeCell ref="D273:D279"/>
+    <mergeCell ref="D285:D289"/>
+    <mergeCell ref="D305:D311"/>
+    <mergeCell ref="D312:D318"/>
+    <mergeCell ref="D400:D401"/>
+    <mergeCell ref="B344:B350"/>
+    <mergeCell ref="D352:D355"/>
+    <mergeCell ref="D356:D359"/>
+    <mergeCell ref="D363:D365"/>
+    <mergeCell ref="D375:D377"/>
+    <mergeCell ref="D378:D380"/>
+    <mergeCell ref="D383:D384"/>
+    <mergeCell ref="D392:D394"/>
+    <mergeCell ref="D395:D397"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D150:D153"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D8:D12"/>
     <mergeCell ref="D16:D18"/>
@@ -7901,35 +7866,6 @@
     <mergeCell ref="D73:D80"/>
     <mergeCell ref="D81:D88"/>
     <mergeCell ref="D95:D98"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="D179:D181"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D400:D401"/>
-    <mergeCell ref="B344:B350"/>
-    <mergeCell ref="D352:D355"/>
-    <mergeCell ref="D356:D359"/>
-    <mergeCell ref="D363:D365"/>
-    <mergeCell ref="D375:D377"/>
-    <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D392:D394"/>
-    <mergeCell ref="D395:D397"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D209:D213"/>
-    <mergeCell ref="D191:D196"/>
-    <mergeCell ref="D227:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="D266:D272"/>
-    <mergeCell ref="D273:D279"/>
-    <mergeCell ref="D285:D289"/>
-    <mergeCell ref="D305:D311"/>
-    <mergeCell ref="D312:D318"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7994,7 +7930,7 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -8012,7 +7948,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="53"/>
+      <c r="D4" s="54"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -8028,7 +7964,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="54"/>
       <c r="E5" s="5" t="s">
         <v>211</v>
       </c>
@@ -8039,7 +7975,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="53"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
@@ -8054,7 +7990,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="54"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="13" t="s">
         <v>207</v>
       </c>
@@ -8069,7 +8005,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="53" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -8082,7 +8018,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -8093,7 +8029,7 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="54"/>
       <c r="E10" s="5" t="s">
         <v>211</v>
       </c>
@@ -8104,7 +8040,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
@@ -8117,7 +8053,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="54"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="13" t="s">
         <v>207</v>
       </c>
@@ -8177,7 +8113,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -8190,7 +8126,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="56"/>
+      <c r="D17" s="57"/>
       <c r="E17" s="5" t="s">
         <v>208</v>
       </c>
@@ -8201,7 +8137,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="57"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="13" t="s">
         <v>134</v>
       </c>
@@ -8359,7 +8295,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -8374,7 +8310,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="54"/>
       <c r="E31" s="5" t="s">
         <v>145</v>
       </c>
@@ -8387,7 +8323,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="54"/>
       <c r="E32" s="5" t="s">
         <v>142</v>
       </c>
@@ -8400,7 +8336,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="54"/>
       <c r="E33" s="5" t="s">
         <v>146</v>
       </c>
@@ -8415,7 +8351,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="54"/>
       <c r="E34" s="5" t="s">
         <v>213</v>
       </c>
@@ -8426,7 +8362,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="5" t="s">
         <v>214</v>
       </c>
@@ -8437,7 +8373,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="54"/>
       <c r="E36" s="5" t="s">
         <v>151</v>
       </c>
@@ -8450,7 +8386,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="54"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="13" t="s">
         <v>210</v>
       </c>
@@ -8467,7 +8403,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -8480,7 +8416,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="54"/>
       <c r="E39" s="5" t="s">
         <v>145</v>
       </c>
@@ -8491,7 +8427,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="54"/>
       <c r="E40" s="5" t="s">
         <v>143</v>
       </c>
@@ -8502,7 +8438,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="5" t="s">
         <v>146</v>
       </c>
@@ -8513,7 +8449,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="54"/>
       <c r="E42" s="5" t="s">
         <v>213</v>
       </c>
@@ -8524,7 +8460,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="5" t="s">
         <v>214</v>
       </c>
@@ -8535,7 +8471,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="54"/>
       <c r="E44" s="5" t="s">
         <v>209</v>
       </c>
@@ -8546,7 +8482,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="54"/>
+      <c r="D45" s="55"/>
       <c r="E45" s="13" t="s">
         <v>210</v>
       </c>
@@ -8643,7 +8579,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -8656,7 +8592,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="56"/>
+      <c r="D53" s="57"/>
       <c r="E53" s="4" t="s">
         <v>147</v>
       </c>
@@ -8667,7 +8603,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="56"/>
+      <c r="D54" s="57"/>
       <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
@@ -8678,7 +8614,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="57"/>
+      <c r="D55" s="58"/>
       <c r="E55" s="13" t="s">
         <v>210</v>
       </c>
@@ -8902,7 +8838,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="52" t="s">
+      <c r="D73" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -8917,7 +8853,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="53"/>
+      <c r="D74" s="54"/>
       <c r="E74" s="5" t="s">
         <v>148</v>
       </c>
@@ -8930,7 +8866,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="53"/>
+      <c r="D75" s="54"/>
       <c r="E75" s="5" t="s">
         <v>153</v>
       </c>
@@ -8943,7 +8879,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="53"/>
+      <c r="D76" s="54"/>
       <c r="E76" s="5" t="s">
         <v>149</v>
       </c>
@@ -8956,7 +8892,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="53"/>
+      <c r="D77" s="54"/>
       <c r="E77" s="5" t="s">
         <v>215</v>
       </c>
@@ -8967,7 +8903,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="53"/>
+      <c r="D78" s="54"/>
       <c r="E78" s="5" t="s">
         <v>216</v>
       </c>
@@ -8978,7 +8914,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="53"/>
+      <c r="D79" s="54"/>
       <c r="E79" s="13" t="s">
         <v>154</v>
       </c>
@@ -8991,7 +8927,7 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="54"/>
+      <c r="D80" s="55"/>
       <c r="E80" s="5" t="s">
         <v>217</v>
       </c>
@@ -9006,7 +8942,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="52" t="s">
+      <c r="D81" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -9019,7 +8955,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="53"/>
+      <c r="D82" s="54"/>
       <c r="E82" s="5" t="s">
         <v>148</v>
       </c>
@@ -9030,7 +8966,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="53"/>
+      <c r="D83" s="54"/>
       <c r="E83" s="5" t="s">
         <v>143</v>
       </c>
@@ -9041,7 +8977,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="53"/>
+      <c r="D84" s="54"/>
       <c r="E84" s="5" t="s">
         <v>149</v>
       </c>
@@ -9052,7 +8988,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="53"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="5" t="s">
         <v>215</v>
       </c>
@@ -9065,7 +9001,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="53"/>
+      <c r="D86" s="54"/>
       <c r="E86" s="5" t="s">
         <v>216</v>
       </c>
@@ -9076,7 +9012,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="53"/>
+      <c r="D87" s="54"/>
       <c r="E87" s="13" t="s">
         <v>154</v>
       </c>
@@ -9087,7 +9023,7 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="54"/>
+      <c r="D88" s="55"/>
       <c r="E88" s="5" t="s">
         <v>217</v>
       </c>
@@ -9182,7 +9118,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="58" t="s">
+      <c r="D95" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -9197,7 +9133,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="56"/>
+      <c r="D96" s="57"/>
       <c r="E96" s="4" t="s">
         <v>150</v>
       </c>
@@ -9208,7 +9144,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="56"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="13" t="s">
         <v>154</v>
       </c>
@@ -9219,7 +9155,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="57"/>
+      <c r="D98" s="58"/>
       <c r="E98" s="5" t="s">
         <v>217</v>
       </c>
@@ -9441,7 +9377,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="52" t="s">
+      <c r="D116" s="53" t="s">
         <v>128</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -9458,7 +9394,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="53"/>
+      <c r="D117" s="54"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -9473,7 +9409,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="54"/>
+      <c r="D118" s="55"/>
       <c r="E118" s="6" t="s">
         <v>156</v>
       </c>
@@ -9488,7 +9424,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="52" t="s">
+      <c r="D119" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -9501,7 +9437,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="53"/>
+      <c r="D120" s="54"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -9512,7 +9448,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="54"/>
+      <c r="D121" s="55"/>
       <c r="E121" s="6" t="s">
         <v>156</v>
       </c>
@@ -9642,7 +9578,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="52" t="s">
+      <c r="D131" s="53" t="s">
         <v>128</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -9659,7 +9595,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="53"/>
+      <c r="D132" s="54"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -9674,7 +9610,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="54"/>
+      <c r="D133" s="55"/>
       <c r="E133" s="6" t="s">
         <v>156</v>
       </c>
@@ -9689,7 +9625,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="52" t="s">
+      <c r="D134" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -9702,7 +9638,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="53"/>
+      <c r="D135" s="54"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -9713,7 +9649,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="54"/>
+      <c r="D136" s="55"/>
       <c r="E136" s="6" t="s">
         <v>156</v>
       </c>
@@ -9843,7 +9779,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="52" t="s">
+      <c r="D146" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -9860,7 +9796,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="53"/>
+      <c r="D147" s="54"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -9873,7 +9809,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="54"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -9884,7 +9820,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="54"/>
+      <c r="D149" s="55"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -9897,7 +9833,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="52" t="s">
+      <c r="D150" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -9910,7 +9846,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="53"/>
+      <c r="D151" s="54"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -9921,7 +9857,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="53"/>
+      <c r="D152" s="54"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -9932,7 +9868,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="54"/>
+      <c r="D153" s="55"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -9984,7 +9920,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="52" t="s">
+      <c r="D157" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -9997,7 +9933,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="53"/>
+      <c r="D158" s="54"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -10008,7 +9944,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="54"/>
+      <c r="D159" s="55"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -10229,7 +10165,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="52" t="s">
+      <c r="D176" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -10244,7 +10180,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="53"/>
+      <c r="D177" s="54"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -10257,7 +10193,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="54"/>
+      <c r="D178" s="55"/>
       <c r="E178" s="6" t="s">
         <v>157</v>
       </c>
@@ -10272,7 +10208,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="52" t="s">
+      <c r="D179" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -10285,7 +10221,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="53"/>
+      <c r="D180" s="54"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -10296,7 +10232,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="54"/>
+      <c r="D181" s="55"/>
       <c r="E181" s="6" t="s">
         <v>157</v>
       </c>
@@ -10430,7 +10366,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="52" t="s">
+      <c r="D191" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -10445,7 +10381,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="53"/>
+      <c r="D192" s="54"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -10458,7 +10394,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="53"/>
+      <c r="D193" s="54"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -10471,7 +10407,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="53"/>
+      <c r="D194" s="54"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -10484,7 +10420,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="53"/>
+      <c r="D195" s="54"/>
       <c r="E195" s="13" t="s">
         <v>48</v>
       </c>
@@ -10499,7 +10435,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="54"/>
+      <c r="D196" s="55"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -10516,7 +10452,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="52" t="s">
+      <c r="D197" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -10529,7 +10465,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="53"/>
+      <c r="D198" s="54"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -10540,7 +10476,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="53"/>
+      <c r="D199" s="54"/>
       <c r="E199" s="6" t="s">
         <v>158</v>
       </c>
@@ -10551,7 +10487,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="53"/>
+      <c r="D200" s="54"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -10562,7 +10498,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="53"/>
+      <c r="D201" s="54"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -10573,7 +10509,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="53"/>
+      <c r="D202" s="54"/>
       <c r="E202" s="13" t="s">
         <v>163</v>
       </c>
@@ -10586,7 +10522,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="54"/>
+      <c r="D203" s="55"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -10674,7 +10610,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="52" t="s">
+      <c r="D209" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -10687,7 +10623,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="53"/>
+      <c r="D210" s="54"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -10698,7 +10634,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="53"/>
+      <c r="D211" s="54"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -10709,7 +10645,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="53"/>
+      <c r="D212" s="54"/>
       <c r="E212" s="13" t="s">
         <v>163</v>
       </c>
@@ -10722,7 +10658,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="54"/>
+      <c r="D213" s="55"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -10906,7 +10842,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="52" t="s">
+      <c r="D227" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -10921,7 +10857,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="53"/>
+      <c r="D228" s="54"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -10934,7 +10870,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="53"/>
+      <c r="D229" s="54"/>
       <c r="E229" s="6" t="s">
         <v>159</v>
       </c>
@@ -10947,7 +10883,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="53"/>
+      <c r="D230" s="54"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -10960,7 +10896,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="53"/>
+      <c r="D231" s="54"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -10973,7 +10909,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="53"/>
+      <c r="D232" s="54"/>
       <c r="E232" s="13" t="s">
         <v>167</v>
       </c>
@@ -10986,7 +10922,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="54"/>
+      <c r="D233" s="55"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -11001,7 +10937,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="52" t="s">
+      <c r="D234" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -11014,7 +10950,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="53"/>
+      <c r="D235" s="54"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -11025,7 +10961,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="53"/>
+      <c r="D236" s="54"/>
       <c r="E236" s="6" t="s">
         <v>159</v>
       </c>
@@ -11036,7 +10972,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="53"/>
+      <c r="D237" s="54"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -11047,7 +10983,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="53"/>
+      <c r="D238" s="54"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -11058,7 +10994,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="53"/>
+      <c r="D239" s="54"/>
       <c r="E239" s="13" t="s">
         <v>167</v>
       </c>
@@ -11069,7 +11005,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="54"/>
+      <c r="D240" s="55"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -11153,7 +11089,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="52" t="s">
+      <c r="D246" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -11166,7 +11102,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="53"/>
+      <c r="D247" s="54"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -11177,7 +11113,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="53"/>
+      <c r="D248" s="54"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -11188,7 +11124,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="53"/>
+      <c r="D249" s="54"/>
       <c r="E249" s="13" t="s">
         <v>167</v>
       </c>
@@ -11199,7 +11135,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="54"/>
+      <c r="D250" s="55"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -11397,7 +11333,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="52" t="s">
+      <c r="D266" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -11412,7 +11348,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="53"/>
+      <c r="D267" s="54"/>
       <c r="E267" s="6" t="s">
         <v>168</v>
       </c>
@@ -11425,7 +11361,7 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="53"/>
+      <c r="D268" s="54"/>
       <c r="E268" s="6" t="s">
         <v>202</v>
       </c>
@@ -11438,7 +11374,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="53"/>
+      <c r="D269" s="54"/>
       <c r="E269" s="6" t="s">
         <v>169</v>
       </c>
@@ -11451,7 +11387,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="53"/>
+      <c r="D270" s="54"/>
       <c r="E270" s="6" t="s">
         <v>170</v>
       </c>
@@ -11464,7 +11400,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="53"/>
+      <c r="D271" s="54"/>
       <c r="E271" s="13" t="s">
         <v>180</v>
       </c>
@@ -11477,7 +11413,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="54"/>
+      <c r="D272" s="55"/>
       <c r="E272" s="13" t="s">
         <v>47</v>
       </c>
@@ -11492,7 +11428,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="52" t="s">
+      <c r="D273" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -11505,7 +11441,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="53"/>
+      <c r="D274" s="54"/>
       <c r="E274" s="6" t="s">
         <v>168</v>
       </c>
@@ -11516,7 +11452,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="53"/>
+      <c r="D275" s="54"/>
       <c r="E275" s="6" t="s">
         <v>202</v>
       </c>
@@ -11527,7 +11463,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="53"/>
+      <c r="D276" s="54"/>
       <c r="E276" s="6" t="s">
         <v>169</v>
       </c>
@@ -11538,7 +11474,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="53"/>
+      <c r="D277" s="54"/>
       <c r="E277" s="6" t="s">
         <v>170</v>
       </c>
@@ -11549,7 +11485,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="53"/>
+      <c r="D278" s="54"/>
       <c r="E278" s="13" t="s">
         <v>180</v>
       </c>
@@ -11560,7 +11496,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="54"/>
+      <c r="D279" s="55"/>
       <c r="E279" s="13" t="s">
         <v>47</v>
       </c>
@@ -11644,7 +11580,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="52" t="s">
+      <c r="D285" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -11657,7 +11593,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="53"/>
+      <c r="D286" s="54"/>
       <c r="E286" s="6" t="s">
         <v>169</v>
       </c>
@@ -11668,7 +11604,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="53"/>
+      <c r="D287" s="54"/>
       <c r="E287" s="6" t="s">
         <v>170</v>
       </c>
@@ -11679,7 +11615,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="53"/>
+      <c r="D288" s="54"/>
       <c r="E288" s="13" t="s">
         <v>180</v>
       </c>
@@ -11690,7 +11626,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="54"/>
+      <c r="D289" s="55"/>
       <c r="E289" s="13" t="s">
         <v>171</v>
       </c>
@@ -11888,7 +11824,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="52" t="s">
+      <c r="D305" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -11903,7 +11839,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="53"/>
+      <c r="D306" s="54"/>
       <c r="E306" s="6" t="s">
         <v>174</v>
       </c>
@@ -11916,7 +11852,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="53"/>
+      <c r="D307" s="54"/>
       <c r="E307" s="6" t="s">
         <v>203</v>
       </c>
@@ -11929,7 +11865,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="53"/>
+      <c r="D308" s="54"/>
       <c r="E308" s="6" t="s">
         <v>175</v>
       </c>
@@ -11942,7 +11878,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="53"/>
+      <c r="D309" s="54"/>
       <c r="E309" s="6" t="s">
         <v>176</v>
       </c>
@@ -11955,7 +11891,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="53"/>
+      <c r="D310" s="54"/>
       <c r="E310" s="45" t="s">
         <v>177</v>
       </c>
@@ -11968,7 +11904,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="54"/>
+      <c r="D311" s="55"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -11983,7 +11919,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="52" t="s">
+      <c r="D312" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -11996,7 +11932,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="53"/>
+      <c r="D313" s="54"/>
       <c r="E313" s="6" t="s">
         <v>174</v>
       </c>
@@ -12007,7 +11943,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="53"/>
+      <c r="D314" s="54"/>
       <c r="E314" s="6" t="s">
         <v>203</v>
       </c>
@@ -12018,7 +11954,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="53"/>
+      <c r="D315" s="54"/>
       <c r="E315" s="6" t="s">
         <v>175</v>
       </c>
@@ -12029,7 +11965,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="53"/>
+      <c r="D316" s="54"/>
       <c r="E316" s="6" t="s">
         <v>176</v>
       </c>
@@ -12040,7 +11976,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="53"/>
+      <c r="D317" s="54"/>
       <c r="E317" s="45" t="s">
         <v>177</v>
       </c>
@@ -12051,7 +11987,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="54"/>
+      <c r="D318" s="55"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -12135,7 +12071,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="52" t="s">
+      <c r="D324" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -12148,7 +12084,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="53"/>
+      <c r="D325" s="54"/>
       <c r="E325" s="6" t="s">
         <v>175</v>
       </c>
@@ -12159,7 +12095,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="53"/>
+      <c r="D326" s="54"/>
       <c r="E326" s="6" t="s">
         <v>176</v>
       </c>
@@ -12170,7 +12106,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="53"/>
+      <c r="D327" s="54"/>
       <c r="E327" s="45" t="s">
         <v>177</v>
       </c>
@@ -12181,7 +12117,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="54"/>
+      <c r="D328" s="55"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -12373,7 +12309,7 @@
     </row>
     <row r="344" spans="1:7" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="55" t="s">
+      <c r="B344" s="59" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -12388,7 +12324,7 @@
     </row>
     <row r="345" spans="1:7" s="9" customFormat="1">
       <c r="A345" s="8"/>
-      <c r="B345" s="56"/>
+      <c r="B345" s="57"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -12399,7 +12335,7 @@
     </row>
     <row r="346" spans="1:7" s="9" customFormat="1">
       <c r="A346" s="8"/>
-      <c r="B346" s="56"/>
+      <c r="B346" s="57"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -12410,7 +12346,7 @@
     </row>
     <row r="347" spans="1:7" s="9" customFormat="1">
       <c r="A347" s="8"/>
-      <c r="B347" s="56"/>
+      <c r="B347" s="57"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -12421,7 +12357,7 @@
     </row>
     <row r="348" spans="1:7" s="9" customFormat="1">
       <c r="A348" s="8"/>
-      <c r="B348" s="56"/>
+      <c r="B348" s="57"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -12432,7 +12368,7 @@
     </row>
     <row r="349" spans="1:7" s="9" customFormat="1">
       <c r="A349" s="8"/>
-      <c r="B349" s="56"/>
+      <c r="B349" s="57"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -12443,7 +12379,7 @@
     </row>
     <row r="350" spans="1:7" s="9" customFormat="1">
       <c r="A350" s="8"/>
-      <c r="B350" s="57"/>
+      <c r="B350" s="58"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -12471,7 +12407,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="52" t="s">
+      <c r="D352" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -12486,7 +12422,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="53"/>
+      <c r="D353" s="54"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -12499,7 +12435,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="53"/>
+      <c r="D354" s="54"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -12512,7 +12448,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="54"/>
+      <c r="D355" s="55"/>
       <c r="E355" s="13" t="s">
         <v>64</v>
       </c>
@@ -12527,7 +12463,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="52" t="s">
+      <c r="D356" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -12540,7 +12476,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="53"/>
+      <c r="D357" s="54"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -12551,7 +12487,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="53"/>
+      <c r="D358" s="54"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -12562,7 +12498,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="54"/>
+      <c r="D359" s="55"/>
       <c r="E359" s="13" t="s">
         <v>64</v>
       </c>
@@ -12618,7 +12554,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="52" t="s">
+      <c r="D363" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -12631,7 +12567,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="53"/>
+      <c r="D364" s="54"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -12642,7 +12578,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="54"/>
+      <c r="D365" s="55"/>
       <c r="E365" s="13" t="s">
         <v>64</v>
       </c>
@@ -12774,7 +12710,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="52" t="s">
+      <c r="D375" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -12789,7 +12725,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="53"/>
+      <c r="D376" s="54"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -12802,7 +12738,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="54"/>
+      <c r="D377" s="55"/>
       <c r="E377" s="46" t="s">
         <v>156</v>
       </c>
@@ -12815,7 +12751,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="52" t="s">
+      <c r="D378" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -12828,7 +12764,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="53"/>
+      <c r="D379" s="54"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -12839,7 +12775,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="54"/>
+      <c r="D380" s="55"/>
       <c r="E380" s="46" t="s">
         <v>156</v>
       </c>
@@ -12880,7 +12816,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="52" t="s">
+      <c r="D383" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -12893,7 +12829,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="54"/>
+      <c r="D384" s="55"/>
       <c r="E384" s="6" t="s">
         <v>160</v>
       </c>
@@ -12989,7 +12925,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="52" t="s">
+      <c r="D392" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -13004,7 +12940,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="53"/>
+      <c r="D393" s="54"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -13017,7 +12953,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="54"/>
+      <c r="D394" s="55"/>
       <c r="E394" s="46" t="s">
         <v>156</v>
       </c>
@@ -13030,7 +12966,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="52" t="s">
+      <c r="D395" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -13043,7 +12979,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="53"/>
+      <c r="D396" s="54"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -13054,7 +12990,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="54"/>
+      <c r="D397" s="55"/>
       <c r="E397" s="46" t="s">
         <v>156</v>
       </c>
@@ -13095,7 +13031,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="52" t="s">
+      <c r="D400" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -13108,7 +13044,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="54"/>
+      <c r="D401" s="55"/>
       <c r="E401" s="6" t="s">
         <v>161</v>
       </c>
@@ -13288,37 +13224,6 @@
     <row r="426" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D285:D289"/>
-    <mergeCell ref="D305:D311"/>
-    <mergeCell ref="D312:D318"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="B344:B350"/>
-    <mergeCell ref="D119:D121"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D73:D80"/>
-    <mergeCell ref="D81:D88"/>
-    <mergeCell ref="D95:D98"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D30:D37"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="D179:D181"/>
-    <mergeCell ref="D191:D196"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D209:D213"/>
-    <mergeCell ref="D227:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="D266:D272"/>
-    <mergeCell ref="D273:D279"/>
     <mergeCell ref="D383:D384"/>
     <mergeCell ref="D392:D394"/>
     <mergeCell ref="D395:D397"/>
@@ -13328,6 +13233,37 @@
     <mergeCell ref="D363:D365"/>
     <mergeCell ref="D375:D377"/>
     <mergeCell ref="D378:D380"/>
+    <mergeCell ref="D227:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="D266:D272"/>
+    <mergeCell ref="D273:D279"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="D191:D196"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D209:D213"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D30:D37"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D73:D80"/>
+    <mergeCell ref="D81:D88"/>
+    <mergeCell ref="D95:D98"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="D285:D289"/>
+    <mergeCell ref="D305:D311"/>
+    <mergeCell ref="D312:D318"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="B344:B350"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13397,7 +13333,7 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -13415,7 +13351,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="53"/>
+      <c r="D4" s="54"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -13431,7 +13367,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="54"/>
       <c r="E5" s="5" t="s">
         <v>211</v>
       </c>
@@ -13442,7 +13378,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="53"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
@@ -13457,7 +13393,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="54"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="13" t="s">
         <v>207</v>
       </c>
@@ -13472,7 +13408,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="53" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -13485,7 +13421,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -13496,7 +13432,7 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="54"/>
       <c r="E10" s="5" t="s">
         <v>211</v>
       </c>
@@ -13507,7 +13443,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
@@ -13520,7 +13456,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="54"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="13" t="s">
         <v>207</v>
       </c>
@@ -13580,7 +13516,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -13593,7 +13529,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="56"/>
+      <c r="D17" s="57"/>
       <c r="E17" s="5" t="s">
         <v>208</v>
       </c>
@@ -13604,7 +13540,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="57"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="13" t="s">
         <v>134</v>
       </c>
@@ -13762,7 +13698,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -13777,7 +13713,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="54"/>
       <c r="E31" s="5" t="s">
         <v>145</v>
       </c>
@@ -13790,7 +13726,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="54"/>
       <c r="E32" s="5" t="s">
         <v>142</v>
       </c>
@@ -13803,7 +13739,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="54"/>
       <c r="E33" s="5" t="s">
         <v>146</v>
       </c>
@@ -13818,7 +13754,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="54"/>
       <c r="E34" s="5" t="s">
         <v>213</v>
       </c>
@@ -13829,7 +13765,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="5" t="s">
         <v>214</v>
       </c>
@@ -13840,7 +13776,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="54"/>
       <c r="E36" s="5" t="s">
         <v>151</v>
       </c>
@@ -13853,7 +13789,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="54"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="13" t="s">
         <v>210</v>
       </c>
@@ -13870,7 +13806,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -13883,7 +13819,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="54"/>
       <c r="E39" s="5" t="s">
         <v>145</v>
       </c>
@@ -13894,7 +13830,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="54"/>
       <c r="E40" s="5" t="s">
         <v>143</v>
       </c>
@@ -13905,7 +13841,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="5" t="s">
         <v>146</v>
       </c>
@@ -13916,7 +13852,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="54"/>
       <c r="E42" s="5" t="s">
         <v>213</v>
       </c>
@@ -13927,7 +13863,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="5" t="s">
         <v>214</v>
       </c>
@@ -13938,7 +13874,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="54"/>
       <c r="E44" s="5" t="s">
         <v>209</v>
       </c>
@@ -13949,7 +13885,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="54"/>
+      <c r="D45" s="55"/>
       <c r="E45" s="13" t="s">
         <v>210</v>
       </c>
@@ -14046,7 +13982,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -14059,7 +13995,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="56"/>
+      <c r="D53" s="57"/>
       <c r="E53" s="4" t="s">
         <v>147</v>
       </c>
@@ -14070,7 +14006,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="56"/>
+      <c r="D54" s="57"/>
       <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
@@ -14081,7 +14017,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="57"/>
+      <c r="D55" s="58"/>
       <c r="E55" s="13" t="s">
         <v>210</v>
       </c>
@@ -14305,7 +14241,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="52" t="s">
+      <c r="D73" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -14320,7 +14256,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="53"/>
+      <c r="D74" s="54"/>
       <c r="E74" s="5" t="s">
         <v>148</v>
       </c>
@@ -14333,7 +14269,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="53"/>
+      <c r="D75" s="54"/>
       <c r="E75" s="5" t="s">
         <v>153</v>
       </c>
@@ -14346,7 +14282,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="53"/>
+      <c r="D76" s="54"/>
       <c r="E76" s="5" t="s">
         <v>149</v>
       </c>
@@ -14359,7 +14295,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="53"/>
+      <c r="D77" s="54"/>
       <c r="E77" s="5" t="s">
         <v>215</v>
       </c>
@@ -14370,7 +14306,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="53"/>
+      <c r="D78" s="54"/>
       <c r="E78" s="5" t="s">
         <v>216</v>
       </c>
@@ -14381,7 +14317,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="53"/>
+      <c r="D79" s="54"/>
       <c r="E79" s="13" t="s">
         <v>154</v>
       </c>
@@ -14394,7 +14330,7 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="54"/>
+      <c r="D80" s="55"/>
       <c r="E80" s="5" t="s">
         <v>217</v>
       </c>
@@ -14409,7 +14345,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="52" t="s">
+      <c r="D81" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -14422,7 +14358,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="53"/>
+      <c r="D82" s="54"/>
       <c r="E82" s="5" t="s">
         <v>148</v>
       </c>
@@ -14433,7 +14369,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="53"/>
+      <c r="D83" s="54"/>
       <c r="E83" s="5" t="s">
         <v>143</v>
       </c>
@@ -14444,7 +14380,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="53"/>
+      <c r="D84" s="54"/>
       <c r="E84" s="5" t="s">
         <v>149</v>
       </c>
@@ -14455,7 +14391,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="53"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="5" t="s">
         <v>215</v>
       </c>
@@ -14468,7 +14404,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="53"/>
+      <c r="D86" s="54"/>
       <c r="E86" s="5" t="s">
         <v>216</v>
       </c>
@@ -14479,7 +14415,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="53"/>
+      <c r="D87" s="54"/>
       <c r="E87" s="13" t="s">
         <v>154</v>
       </c>
@@ -14490,7 +14426,7 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="54"/>
+      <c r="D88" s="55"/>
       <c r="E88" s="5" t="s">
         <v>217</v>
       </c>
@@ -14585,7 +14521,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="58" t="s">
+      <c r="D95" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -14600,7 +14536,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="56"/>
+      <c r="D96" s="57"/>
       <c r="E96" s="4" t="s">
         <v>150</v>
       </c>
@@ -14611,7 +14547,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="56"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="13" t="s">
         <v>154</v>
       </c>
@@ -14622,7 +14558,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="57"/>
+      <c r="D98" s="58"/>
       <c r="E98" s="5" t="s">
         <v>217</v>
       </c>
@@ -14844,7 +14780,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="52" t="s">
+      <c r="D116" s="53" t="s">
         <v>128</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -14861,7 +14797,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="53"/>
+      <c r="D117" s="54"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -14876,7 +14812,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="54"/>
+      <c r="D118" s="55"/>
       <c r="E118" s="6" t="s">
         <v>156</v>
       </c>
@@ -14891,7 +14827,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="52" t="s">
+      <c r="D119" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -14904,7 +14840,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="53"/>
+      <c r="D120" s="54"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -14915,7 +14851,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="54"/>
+      <c r="D121" s="55"/>
       <c r="E121" s="6" t="s">
         <v>156</v>
       </c>
@@ -15045,7 +14981,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="52" t="s">
+      <c r="D131" s="53" t="s">
         <v>128</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -15062,7 +14998,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="53"/>
+      <c r="D132" s="54"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -15077,7 +15013,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="54"/>
+      <c r="D133" s="55"/>
       <c r="E133" s="6" t="s">
         <v>156</v>
       </c>
@@ -15092,7 +15028,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="52" t="s">
+      <c r="D134" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -15105,7 +15041,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="53"/>
+      <c r="D135" s="54"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -15116,7 +15052,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="54"/>
+      <c r="D136" s="55"/>
       <c r="E136" s="6" t="s">
         <v>156</v>
       </c>
@@ -15246,7 +15182,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="52" t="s">
+      <c r="D146" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -15263,7 +15199,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="53"/>
+      <c r="D147" s="54"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -15276,7 +15212,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="53"/>
+      <c r="D148" s="54"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -15287,7 +15223,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="54"/>
+      <c r="D149" s="55"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -15300,7 +15236,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="52" t="s">
+      <c r="D150" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -15313,7 +15249,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="53"/>
+      <c r="D151" s="54"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -15324,7 +15260,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="53"/>
+      <c r="D152" s="54"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -15335,7 +15271,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="54"/>
+      <c r="D153" s="55"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -15387,7 +15323,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="52" t="s">
+      <c r="D157" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -15400,7 +15336,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="53"/>
+      <c r="D158" s="54"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -15411,7 +15347,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="54"/>
+      <c r="D159" s="55"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -15632,7 +15568,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="52" t="s">
+      <c r="D176" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -15647,7 +15583,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="53"/>
+      <c r="D177" s="54"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -15660,7 +15596,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="54"/>
+      <c r="D178" s="55"/>
       <c r="E178" s="6" t="s">
         <v>157</v>
       </c>
@@ -15675,7 +15611,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="52" t="s">
+      <c r="D179" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -15688,7 +15624,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="53"/>
+      <c r="D180" s="54"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -15699,7 +15635,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="54"/>
+      <c r="D181" s="55"/>
       <c r="E181" s="6" t="s">
         <v>157</v>
       </c>
@@ -15833,7 +15769,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="52" t="s">
+      <c r="D191" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -15848,7 +15784,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="53"/>
+      <c r="D192" s="54"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -15861,7 +15797,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="53"/>
+      <c r="D193" s="54"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -15874,7 +15810,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="53"/>
+      <c r="D194" s="54"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -15887,7 +15823,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="53"/>
+      <c r="D195" s="54"/>
       <c r="E195" s="13" t="s">
         <v>48</v>
       </c>
@@ -15902,7 +15838,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="54"/>
+      <c r="D196" s="55"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -15919,7 +15855,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="52" t="s">
+      <c r="D197" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -15932,7 +15868,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="53"/>
+      <c r="D198" s="54"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -15943,7 +15879,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="53"/>
+      <c r="D199" s="54"/>
       <c r="E199" s="6" t="s">
         <v>158</v>
       </c>
@@ -15954,7 +15890,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="53"/>
+      <c r="D200" s="54"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -15965,7 +15901,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="53"/>
+      <c r="D201" s="54"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -15976,7 +15912,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="53"/>
+      <c r="D202" s="54"/>
       <c r="E202" s="13" t="s">
         <v>163</v>
       </c>
@@ -15989,7 +15925,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="54"/>
+      <c r="D203" s="55"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -16077,7 +16013,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="52" t="s">
+      <c r="D209" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -16090,7 +16026,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="53"/>
+      <c r="D210" s="54"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -16101,7 +16037,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="53"/>
+      <c r="D211" s="54"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -16112,7 +16048,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="53"/>
+      <c r="D212" s="54"/>
       <c r="E212" s="13" t="s">
         <v>163</v>
       </c>
@@ -16125,7 +16061,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="54"/>
+      <c r="D213" s="55"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -16309,7 +16245,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="52" t="s">
+      <c r="D227" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -16324,7 +16260,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="53"/>
+      <c r="D228" s="54"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -16337,7 +16273,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="53"/>
+      <c r="D229" s="54"/>
       <c r="E229" s="6" t="s">
         <v>159</v>
       </c>
@@ -16350,7 +16286,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="53"/>
+      <c r="D230" s="54"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -16363,7 +16299,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="53"/>
+      <c r="D231" s="54"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -16376,7 +16312,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="53"/>
+      <c r="D232" s="54"/>
       <c r="E232" s="13" t="s">
         <v>167</v>
       </c>
@@ -16389,7 +16325,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="54"/>
+      <c r="D233" s="55"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -16404,7 +16340,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="52" t="s">
+      <c r="D234" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -16417,7 +16353,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="53"/>
+      <c r="D235" s="54"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -16428,7 +16364,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="53"/>
+      <c r="D236" s="54"/>
       <c r="E236" s="6" t="s">
         <v>159</v>
       </c>
@@ -16439,7 +16375,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="53"/>
+      <c r="D237" s="54"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -16450,7 +16386,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="53"/>
+      <c r="D238" s="54"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -16461,7 +16397,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="53"/>
+      <c r="D239" s="54"/>
       <c r="E239" s="13" t="s">
         <v>167</v>
       </c>
@@ -16472,7 +16408,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="54"/>
+      <c r="D240" s="55"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -16556,7 +16492,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="52" t="s">
+      <c r="D246" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -16569,7 +16505,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="53"/>
+      <c r="D247" s="54"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -16580,7 +16516,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="53"/>
+      <c r="D248" s="54"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -16591,7 +16527,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="53"/>
+      <c r="D249" s="54"/>
       <c r="E249" s="13" t="s">
         <v>167</v>
       </c>
@@ -16602,7 +16538,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="54"/>
+      <c r="D250" s="55"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -16800,7 +16736,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="52" t="s">
+      <c r="D266" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -16815,7 +16751,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="53"/>
+      <c r="D267" s="54"/>
       <c r="E267" s="6" t="s">
         <v>168</v>
       </c>
@@ -16828,7 +16764,7 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="53"/>
+      <c r="D268" s="54"/>
       <c r="E268" s="6" t="s">
         <v>202</v>
       </c>
@@ -16841,7 +16777,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="53"/>
+      <c r="D269" s="54"/>
       <c r="E269" s="6" t="s">
         <v>169</v>
       </c>
@@ -16854,7 +16790,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="53"/>
+      <c r="D270" s="54"/>
       <c r="E270" s="6" t="s">
         <v>170</v>
       </c>
@@ -16867,7 +16803,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="53"/>
+      <c r="D271" s="54"/>
       <c r="E271" s="13" t="s">
         <v>180</v>
       </c>
@@ -16880,7 +16816,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="54"/>
+      <c r="D272" s="55"/>
       <c r="E272" s="13" t="s">
         <v>47</v>
       </c>
@@ -16895,7 +16831,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="52" t="s">
+      <c r="D273" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -16908,7 +16844,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="53"/>
+      <c r="D274" s="54"/>
       <c r="E274" s="6" t="s">
         <v>168</v>
       </c>
@@ -16919,7 +16855,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="53"/>
+      <c r="D275" s="54"/>
       <c r="E275" s="6" t="s">
         <v>202</v>
       </c>
@@ -16930,7 +16866,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="53"/>
+      <c r="D276" s="54"/>
       <c r="E276" s="6" t="s">
         <v>169</v>
       </c>
@@ -16941,7 +16877,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="53"/>
+      <c r="D277" s="54"/>
       <c r="E277" s="6" t="s">
         <v>170</v>
       </c>
@@ -16952,7 +16888,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="53"/>
+      <c r="D278" s="54"/>
       <c r="E278" s="13" t="s">
         <v>180</v>
       </c>
@@ -16963,7 +16899,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="54"/>
+      <c r="D279" s="55"/>
       <c r="E279" s="13" t="s">
         <v>47</v>
       </c>
@@ -17047,7 +16983,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="52" t="s">
+      <c r="D285" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -17060,7 +16996,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="53"/>
+      <c r="D286" s="54"/>
       <c r="E286" s="6" t="s">
         <v>169</v>
       </c>
@@ -17071,7 +17007,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="53"/>
+      <c r="D287" s="54"/>
       <c r="E287" s="6" t="s">
         <v>170</v>
       </c>
@@ -17082,7 +17018,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="53"/>
+      <c r="D288" s="54"/>
       <c r="E288" s="13" t="s">
         <v>180</v>
       </c>
@@ -17093,7 +17029,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="54"/>
+      <c r="D289" s="55"/>
       <c r="E289" s="13" t="s">
         <v>171</v>
       </c>
@@ -17291,7 +17227,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="52" t="s">
+      <c r="D305" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -17306,7 +17242,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="53"/>
+      <c r="D306" s="54"/>
       <c r="E306" s="6" t="s">
         <v>174</v>
       </c>
@@ -17319,7 +17255,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="53"/>
+      <c r="D307" s="54"/>
       <c r="E307" s="6" t="s">
         <v>203</v>
       </c>
@@ -17332,7 +17268,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="53"/>
+      <c r="D308" s="54"/>
       <c r="E308" s="6" t="s">
         <v>175</v>
       </c>
@@ -17345,7 +17281,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="53"/>
+      <c r="D309" s="54"/>
       <c r="E309" s="6" t="s">
         <v>176</v>
       </c>
@@ -17358,7 +17294,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="53"/>
+      <c r="D310" s="54"/>
       <c r="E310" s="45" t="s">
         <v>177</v>
       </c>
@@ -17371,7 +17307,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="54"/>
+      <c r="D311" s="55"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -17386,7 +17322,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="52" t="s">
+      <c r="D312" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -17399,7 +17335,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="53"/>
+      <c r="D313" s="54"/>
       <c r="E313" s="6" t="s">
         <v>174</v>
       </c>
@@ -17410,7 +17346,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="53"/>
+      <c r="D314" s="54"/>
       <c r="E314" s="6" t="s">
         <v>203</v>
       </c>
@@ -17421,7 +17357,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="53"/>
+      <c r="D315" s="54"/>
       <c r="E315" s="6" t="s">
         <v>175</v>
       </c>
@@ -17432,7 +17368,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="53"/>
+      <c r="D316" s="54"/>
       <c r="E316" s="6" t="s">
         <v>176</v>
       </c>
@@ -17443,7 +17379,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="53"/>
+      <c r="D317" s="54"/>
       <c r="E317" s="45" t="s">
         <v>177</v>
       </c>
@@ -17454,7 +17390,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="54"/>
+      <c r="D318" s="55"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -17538,7 +17474,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="52" t="s">
+      <c r="D324" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -17551,7 +17487,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="53"/>
+      <c r="D325" s="54"/>
       <c r="E325" s="6" t="s">
         <v>175</v>
       </c>
@@ -17562,7 +17498,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="53"/>
+      <c r="D326" s="54"/>
       <c r="E326" s="6" t="s">
         <v>176</v>
       </c>
@@ -17573,7 +17509,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="53"/>
+      <c r="D327" s="54"/>
       <c r="E327" s="45" t="s">
         <v>177</v>
       </c>
@@ -17584,7 +17520,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="54"/>
+      <c r="D328" s="55"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -17776,7 +17712,7 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="8"/>
-      <c r="B344" s="55" t="s">
+      <c r="B344" s="59" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -17791,7 +17727,7 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="8"/>
-      <c r="B345" s="56"/>
+      <c r="B345" s="57"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -17802,7 +17738,7 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="8"/>
-      <c r="B346" s="56"/>
+      <c r="B346" s="57"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -17813,7 +17749,7 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="8"/>
-      <c r="B347" s="56"/>
+      <c r="B347" s="57"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -17824,7 +17760,7 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="8"/>
-      <c r="B348" s="56"/>
+      <c r="B348" s="57"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -17835,7 +17771,7 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="8"/>
-      <c r="B349" s="56"/>
+      <c r="B349" s="57"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -17846,7 +17782,7 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="8"/>
-      <c r="B350" s="57"/>
+      <c r="B350" s="58"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -17874,7 +17810,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="52" t="s">
+      <c r="D352" s="53" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -17889,7 +17825,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="53"/>
+      <c r="D353" s="54"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -17902,7 +17838,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="53"/>
+      <c r="D354" s="54"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -17915,7 +17851,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="54"/>
+      <c r="D355" s="55"/>
       <c r="E355" s="13" t="s">
         <v>64</v>
       </c>
@@ -17930,7 +17866,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="52" t="s">
+      <c r="D356" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -17943,7 +17879,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="53"/>
+      <c r="D357" s="54"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -17954,7 +17890,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="53"/>
+      <c r="D358" s="54"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -17965,7 +17901,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="54"/>
+      <c r="D359" s="55"/>
       <c r="E359" s="13" t="s">
         <v>64</v>
       </c>
@@ -18021,7 +17957,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="52" t="s">
+      <c r="D363" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -18034,7 +17970,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="53"/>
+      <c r="D364" s="54"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -18045,7 +17981,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="54"/>
+      <c r="D365" s="55"/>
       <c r="E365" s="13" t="s">
         <v>64</v>
       </c>
@@ -18177,7 +18113,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="52" t="s">
+      <c r="D375" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -18192,7 +18128,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="53"/>
+      <c r="D376" s="54"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -18205,7 +18141,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="54"/>
+      <c r="D377" s="55"/>
       <c r="E377" s="46" t="s">
         <v>156</v>
       </c>
@@ -18218,7 +18154,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="52" t="s">
+      <c r="D378" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -18231,7 +18167,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="53"/>
+      <c r="D379" s="54"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -18242,7 +18178,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="54"/>
+      <c r="D380" s="55"/>
       <c r="E380" s="46" t="s">
         <v>156</v>
       </c>
@@ -18283,7 +18219,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="52" t="s">
+      <c r="D383" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -18296,7 +18232,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="54"/>
+      <c r="D384" s="55"/>
       <c r="E384" s="6" t="s">
         <v>160</v>
       </c>
@@ -18392,7 +18328,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="52" t="s">
+      <c r="D392" s="53" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -18407,7 +18343,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="53"/>
+      <c r="D393" s="54"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -18420,7 +18356,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="54"/>
+      <c r="D394" s="55"/>
       <c r="E394" s="46" t="s">
         <v>156</v>
       </c>
@@ -18433,7 +18369,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="52" t="s">
+      <c r="D395" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -18446,7 +18382,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="53"/>
+      <c r="D396" s="54"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -18457,7 +18393,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="54"/>
+      <c r="D397" s="55"/>
       <c r="E397" s="46" t="s">
         <v>156</v>
       </c>
@@ -18498,7 +18434,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="52" t="s">
+      <c r="D400" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -18511,7 +18447,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="54"/>
+      <c r="D401" s="55"/>
       <c r="E401" s="6" t="s">
         <v>161</v>
       </c>
@@ -18688,16 +18624,21 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B344:B350"/>
-    <mergeCell ref="D352:D355"/>
-    <mergeCell ref="D356:D359"/>
-    <mergeCell ref="D363:D365"/>
-    <mergeCell ref="D375:D377"/>
-    <mergeCell ref="D209:D213"/>
-    <mergeCell ref="D227:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="D266:D272"/>
+    <mergeCell ref="D378:D380"/>
+    <mergeCell ref="D383:D384"/>
+    <mergeCell ref="D392:D394"/>
+    <mergeCell ref="D395:D397"/>
+    <mergeCell ref="D400:D401"/>
+    <mergeCell ref="D273:D279"/>
+    <mergeCell ref="D285:D289"/>
+    <mergeCell ref="D305:D311"/>
+    <mergeCell ref="D312:D318"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D191:D196"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D157:D159"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D8:D12"/>
     <mergeCell ref="D16:D18"/>
@@ -18713,21 +18654,16 @@
     <mergeCell ref="D119:D121"/>
     <mergeCell ref="D131:D133"/>
     <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D191:D196"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D273:D279"/>
-    <mergeCell ref="D285:D289"/>
-    <mergeCell ref="D305:D311"/>
-    <mergeCell ref="D312:D318"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D392:D394"/>
-    <mergeCell ref="D395:D397"/>
-    <mergeCell ref="D400:D401"/>
+    <mergeCell ref="D209:D213"/>
+    <mergeCell ref="D227:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="D266:D272"/>
+    <mergeCell ref="B344:B350"/>
+    <mergeCell ref="D352:D355"/>
+    <mergeCell ref="D356:D359"/>
+    <mergeCell ref="D363:D365"/>
+    <mergeCell ref="D375:D377"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19167,7 +19103,7 @@
     <row r="29" spans="1:6">
       <c r="A29" s="18"/>
       <c r="B29" s="26" t="s">
-        <v>156</v>
+        <v>325</v>
       </c>
       <c r="C29" s="44" t="s">
         <v>156</v>
@@ -19852,104 +19788,104 @@
       <c r="A74" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B74" s="61" t="s">
+      <c r="B74" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="62"/>
+      <c r="C74" s="62"/>
+      <c r="D74" s="62"/>
+      <c r="E74" s="63"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="15"/>
-      <c r="B75" s="59" t="s">
+      <c r="B75" s="60" t="s">
         <v>232</v>
       </c>
-      <c r="C75" s="59"/>
-      <c r="D75" s="59"/>
-      <c r="E75" s="60"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="61"/>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="15"/>
-      <c r="B76" s="59" t="s">
+      <c r="B76" s="60" t="s">
         <v>233</v>
       </c>
-      <c r="C76" s="59"/>
-      <c r="D76" s="59"/>
-      <c r="E76" s="60"/>
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="61"/>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="15"/>
-      <c r="B77" s="59" t="s">
+      <c r="B77" s="60" t="s">
         <v>234</v>
       </c>
-      <c r="C77" s="59"/>
-      <c r="D77" s="59"/>
-      <c r="E77" s="60"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="61"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="15"/>
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="60" t="s">
         <v>235</v>
       </c>
-      <c r="C78" s="59"/>
-      <c r="D78" s="59"/>
-      <c r="E78" s="60"/>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="61"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="15"/>
-      <c r="B79" s="59" t="s">
+      <c r="B79" s="60" t="s">
         <v>236</v>
       </c>
-      <c r="C79" s="59"/>
-      <c r="D79" s="59"/>
-      <c r="E79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="61"/>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="18"/>
-      <c r="B80" s="59" t="s">
+      <c r="B80" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="C80" s="59"/>
-      <c r="D80" s="59"/>
-      <c r="E80" s="60"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="61"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B81" s="61" t="s">
+      <c r="B81" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-      <c r="E81" s="62"/>
+      <c r="C81" s="62"/>
+      <c r="D81" s="62"/>
+      <c r="E81" s="63"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="15"/>
-      <c r="B82" s="59" t="s">
+      <c r="B82" s="60" t="s">
         <v>323</v>
       </c>
-      <c r="C82" s="59"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="60"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="61"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="15"/>
-      <c r="B83" s="59" t="s">
+      <c r="B83" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="C83" s="59"/>
-      <c r="D83" s="59"/>
-      <c r="E83" s="60"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="61"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="18"/>
-      <c r="B84" s="63" t="s">
+      <c r="B84" s="64" t="s">
         <v>239</v>
       </c>
-      <c r="C84" s="63"/>
-      <c r="D84" s="63"/>
-      <c r="E84" s="64"/>
+      <c r="C84" s="64"/>
+      <c r="D84" s="64"/>
+      <c r="E84" s="65"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
@@ -19958,17 +19894,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B83:E83"/>
     <mergeCell ref="B79:E79"/>
     <mergeCell ref="B74:E74"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B83:E83"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20626,118 +20562,118 @@
       <c r="A40" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="61" t="s">
+      <c r="B40" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="63"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="15"/>
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="60" t="s">
         <v>232</v>
       </c>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="15"/>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="60" t="s">
         <v>233</v>
       </c>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="61"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="15"/>
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="60" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="60"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="61"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="15"/>
-      <c r="B44" s="59" t="s">
+      <c r="B44" s="60" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="61"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="15"/>
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="60" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="61"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="18"/>
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="60"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="61"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B47" s="61" t="s">
+      <c r="B47" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="62"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="63"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="15"/>
-      <c r="B48" s="59" t="s">
+      <c r="B48" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="60"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="60"/>
+      <c r="E48" s="61"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="15"/>
-      <c r="B49" s="59" t="s">
+      <c r="B49" s="60" t="s">
         <v>230</v>
       </c>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="60"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="61"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="18"/>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="C50" s="63"/>
-      <c r="D50" s="63"/>
-      <c r="E50" s="64"/>
+      <c r="C50" s="64"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
